--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ281"/>
+  <dimension ref="A1:AZ280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16524,10 +16524,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130996947</v>
+        <v>128146055</v>
       </c>
       <c r="B139" t="n">
-        <v>87345</v>
+        <v>93189</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16535,37 +16535,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3746</v>
+        <v>4361</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gulblå spindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius transiens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Melot) Soop</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>691080</v>
+        <v>690845</v>
       </c>
       <c r="R139" t="n">
-        <v>7401099</v>
+        <v>7400680</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16592,17 +16589,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>DNA-sekvens av Petra Wikströms rapport https://www.artportalen.se/Sighting/128960678.</t>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16611,35 +16613,30 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130996947</t>
+          <t>https://artportalen.se/Sighting/128146055</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128146055</v>
+        <v>128146056</v>
       </c>
       <c r="B140" t="n">
         <v>93189</v>
@@ -16674,10 +16671,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>690845</v>
+        <v>690781</v>
       </c>
       <c r="R140" t="n">
-        <v>7400680</v>
+        <v>7400555</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16709,7 +16706,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16719,7 +16716,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16745,13 +16742,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146055</t>
+          <t>https://artportalen.se/Sighting/128146056</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128146056</v>
+        <v>128146057</v>
       </c>
       <c r="B141" t="n">
         <v>93189</v>
@@ -16786,10 +16783,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>690781</v>
+        <v>690810</v>
       </c>
       <c r="R141" t="n">
-        <v>7400555</v>
+        <v>7400772</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16821,7 +16818,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16831,7 +16828,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16857,16 +16854,16 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146056</t>
+          <t>https://artportalen.se/Sighting/128146057</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128146057</v>
+        <v>128146074</v>
       </c>
       <c r="B142" t="n">
-        <v>93189</v>
+        <v>93191</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16874,21 +16871,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16898,10 +16895,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>690810</v>
+        <v>690796</v>
       </c>
       <c r="R142" t="n">
-        <v>7400772</v>
+        <v>7400787</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16933,7 +16930,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16943,7 +16940,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16969,16 +16966,16 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146057</t>
+          <t>https://artportalen.se/Sighting/128146074</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128146074</v>
+        <v>128102520</v>
       </c>
       <c r="B143" t="n">
-        <v>93191</v>
+        <v>93197</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16986,34 +16983,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>690796</v>
+        <v>690800</v>
       </c>
       <c r="R143" t="n">
-        <v>7400787</v>
+        <v>7400819</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17043,19 +17040,9 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17081,13 +17068,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146074</t>
+          <t>https://artportalen.se/Sighting/128102520</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128102520</v>
+        <v>128144837</v>
       </c>
       <c r="B144" t="n">
         <v>93197</v>
@@ -17118,14 +17105,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>690800</v>
+        <v>691657</v>
       </c>
       <c r="R144" t="n">
-        <v>7400819</v>
+        <v>7400758</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17155,9 +17142,19 @@
           <t>2025-08-31</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17183,13 +17180,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128102520</t>
+          <t>https://artportalen.se/Sighting/128144837</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128144837</v>
+        <v>128146066</v>
       </c>
       <c r="B145" t="n">
         <v>93197</v>
@@ -17224,10 +17221,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>691657</v>
+        <v>691535</v>
       </c>
       <c r="R145" t="n">
-        <v>7400758</v>
+        <v>7400857</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17259,7 +17256,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17269,7 +17266,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17295,13 +17292,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144837</t>
+          <t>https://artportalen.se/Sighting/128146066</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128146066</v>
+        <v>128146067</v>
       </c>
       <c r="B146" t="n">
         <v>93197</v>
@@ -17336,10 +17333,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>691535</v>
+        <v>691067</v>
       </c>
       <c r="R146" t="n">
-        <v>7400857</v>
+        <v>7400865</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17371,7 +17368,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17381,7 +17378,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17407,13 +17404,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146066</t>
+          <t>https://artportalen.se/Sighting/128146067</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128146067</v>
+        <v>128146068</v>
       </c>
       <c r="B147" t="n">
         <v>93197</v>
@@ -17448,10 +17445,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>691067</v>
+        <v>691003</v>
       </c>
       <c r="R147" t="n">
-        <v>7400865</v>
+        <v>7400832</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17483,7 +17480,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17493,7 +17490,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17519,13 +17516,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146067</t>
+          <t>https://artportalen.se/Sighting/128146068</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128146068</v>
+        <v>128146069</v>
       </c>
       <c r="B148" t="n">
         <v>93197</v>
@@ -17563,7 +17560,7 @@
         <v>691003</v>
       </c>
       <c r="R148" t="n">
-        <v>7400832</v>
+        <v>7400833</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17631,13 +17628,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146068</t>
+          <t>https://artportalen.se/Sighting/128146069</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128146069</v>
+        <v>128146070</v>
       </c>
       <c r="B149" t="n">
         <v>93197</v>
@@ -17672,10 +17669,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>691003</v>
+        <v>690846</v>
       </c>
       <c r="R149" t="n">
-        <v>7400833</v>
+        <v>7400687</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17707,7 +17704,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17717,7 +17714,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17743,13 +17740,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146069</t>
+          <t>https://artportalen.se/Sighting/128146070</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128146070</v>
+        <v>128146071</v>
       </c>
       <c r="B150" t="n">
         <v>93197</v>
@@ -17784,10 +17781,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>690846</v>
+        <v>690800</v>
       </c>
       <c r="R150" t="n">
-        <v>7400687</v>
+        <v>7400737</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17819,7 +17816,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17829,7 +17826,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17855,13 +17852,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146070</t>
+          <t>https://artportalen.se/Sighting/128146071</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128146071</v>
+        <v>128960626</v>
       </c>
       <c r="B151" t="n">
         <v>93197</v>
@@ -17892,14 +17889,14 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>690800</v>
+        <v>691772</v>
       </c>
       <c r="R151" t="n">
-        <v>7400737</v>
+        <v>7400877</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17926,22 +17923,22 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17956,24 +17953,28 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146071</t>
+          <t>https://artportalen.se/Sighting/128960626</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128960626</v>
+        <v>128960629</v>
       </c>
       <c r="B152" t="n">
         <v>93197</v>
@@ -18008,10 +18009,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>691772</v>
+        <v>691778</v>
       </c>
       <c r="R152" t="n">
-        <v>7400877</v>
+        <v>7401031</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18043,7 +18044,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18053,7 +18054,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18083,13 +18084,13 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960626</t>
+          <t>https://artportalen.se/Sighting/128960629</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128960629</v>
+        <v>128960631</v>
       </c>
       <c r="B153" t="n">
         <v>93197</v>
@@ -18124,10 +18125,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>691778</v>
+        <v>691572</v>
       </c>
       <c r="R153" t="n">
-        <v>7401031</v>
+        <v>7401097</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18159,7 +18160,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18169,7 +18170,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18199,13 +18200,13 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960629</t>
+          <t>https://artportalen.se/Sighting/128960631</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128960631</v>
+        <v>128960633</v>
       </c>
       <c r="B154" t="n">
         <v>93197</v>
@@ -18240,10 +18241,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>691572</v>
+        <v>691476</v>
       </c>
       <c r="R154" t="n">
-        <v>7401097</v>
+        <v>7400909</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18275,7 +18276,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18285,7 +18286,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18315,13 +18316,13 @@
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960631</t>
+          <t>https://artportalen.se/Sighting/128960633</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128960633</v>
+        <v>128960634</v>
       </c>
       <c r="B155" t="n">
         <v>93197</v>
@@ -18356,10 +18357,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>691476</v>
+        <v>691432</v>
       </c>
       <c r="R155" t="n">
-        <v>7400909</v>
+        <v>7400884</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18391,7 +18392,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18401,7 +18402,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18431,13 +18432,13 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960633</t>
+          <t>https://artportalen.se/Sighting/128960634</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128960634</v>
+        <v>128960636</v>
       </c>
       <c r="B156" t="n">
         <v>93197</v>
@@ -18472,10 +18473,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>691432</v>
+        <v>691313</v>
       </c>
       <c r="R156" t="n">
-        <v>7400884</v>
+        <v>7400890</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18507,7 +18508,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18517,7 +18518,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18547,13 +18548,13 @@
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960634</t>
+          <t>https://artportalen.se/Sighting/128960636</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128960636</v>
+        <v>128960637</v>
       </c>
       <c r="B157" t="n">
         <v>93197</v>
@@ -18588,10 +18589,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>691313</v>
+        <v>691085</v>
       </c>
       <c r="R157" t="n">
-        <v>7400890</v>
+        <v>7400630</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18623,7 +18624,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18633,7 +18634,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18663,13 +18664,13 @@
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960636</t>
+          <t>https://artportalen.se/Sighting/128960637</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128960637</v>
+        <v>128960639</v>
       </c>
       <c r="B158" t="n">
         <v>93197</v>
@@ -18704,10 +18705,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>691085</v>
+        <v>691173</v>
       </c>
       <c r="R158" t="n">
-        <v>7400630</v>
+        <v>7400751</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18739,7 +18740,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18749,7 +18750,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18779,13 +18780,13 @@
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960637</t>
+          <t>https://artportalen.se/Sighting/128960639</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128960639</v>
+        <v>128960641</v>
       </c>
       <c r="B159" t="n">
         <v>93197</v>
@@ -18820,10 +18821,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>691173</v>
+        <v>691271</v>
       </c>
       <c r="R159" t="n">
-        <v>7400751</v>
+        <v>7400775</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18855,7 +18856,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18865,7 +18866,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18895,13 +18896,13 @@
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960639</t>
+          <t>https://artportalen.se/Sighting/128960641</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128960641</v>
+        <v>128960642</v>
       </c>
       <c r="B160" t="n">
         <v>93197</v>
@@ -18936,10 +18937,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>691271</v>
+        <v>691479</v>
       </c>
       <c r="R160" t="n">
-        <v>7400775</v>
+        <v>7400776</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18971,7 +18972,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18981,7 +18982,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19011,13 +19012,13 @@
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960641</t>
+          <t>https://artportalen.se/Sighting/128960642</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128960642</v>
+        <v>128960644</v>
       </c>
       <c r="B161" t="n">
         <v>93197</v>
@@ -19052,10 +19053,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>691479</v>
+        <v>691471</v>
       </c>
       <c r="R161" t="n">
-        <v>7400776</v>
+        <v>7400823</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19087,7 +19088,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19097,7 +19098,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19127,13 +19128,13 @@
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960642</t>
+          <t>https://artportalen.se/Sighting/128960644</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128960644</v>
+        <v>128960646</v>
       </c>
       <c r="B162" t="n">
         <v>93197</v>
@@ -19168,10 +19169,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>691471</v>
+        <v>691445</v>
       </c>
       <c r="R162" t="n">
-        <v>7400823</v>
+        <v>7400907</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19203,7 +19204,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19213,7 +19214,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19243,13 +19244,13 @@
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960644</t>
+          <t>https://artportalen.se/Sighting/128960646</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128960646</v>
+        <v>128960650</v>
       </c>
       <c r="B163" t="n">
         <v>93197</v>
@@ -19284,10 +19285,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>691445</v>
+        <v>690728</v>
       </c>
       <c r="R163" t="n">
-        <v>7400907</v>
+        <v>7400633</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19314,22 +19315,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19359,13 +19360,13 @@
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960646</t>
+          <t>https://artportalen.se/Sighting/128960650</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128960650</v>
+        <v>128960653</v>
       </c>
       <c r="B164" t="n">
         <v>93197</v>
@@ -19400,10 +19401,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>690728</v>
+        <v>690703</v>
       </c>
       <c r="R164" t="n">
-        <v>7400633</v>
+        <v>7400802</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19435,7 +19436,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19445,7 +19446,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19475,13 +19476,13 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960650</t>
+          <t>https://artportalen.se/Sighting/128960653</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128960653</v>
+        <v>128960655</v>
       </c>
       <c r="B165" t="n">
         <v>93197</v>
@@ -19516,10 +19517,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>690703</v>
+        <v>690734</v>
       </c>
       <c r="R165" t="n">
-        <v>7400802</v>
+        <v>7400797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19551,7 +19552,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19561,7 +19562,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19591,13 +19592,13 @@
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960653</t>
+          <t>https://artportalen.se/Sighting/128960655</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128960655</v>
+        <v>128960658</v>
       </c>
       <c r="B166" t="n">
         <v>93197</v>
@@ -19632,10 +19633,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>690734</v>
+        <v>690788</v>
       </c>
       <c r="R166" t="n">
-        <v>7400797</v>
+        <v>7400864</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19667,7 +19668,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19677,7 +19678,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19707,13 +19708,13 @@
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960655</t>
+          <t>https://artportalen.se/Sighting/128960658</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128960658</v>
+        <v>128960661</v>
       </c>
       <c r="B167" t="n">
         <v>93197</v>
@@ -19748,10 +19749,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>690788</v>
+        <v>691007</v>
       </c>
       <c r="R167" t="n">
-        <v>7400864</v>
+        <v>7401047</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19783,7 +19784,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19793,7 +19794,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19823,16 +19824,16 @@
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960658</t>
+          <t>https://artportalen.se/Sighting/128960661</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128960661</v>
+        <v>128960416</v>
       </c>
       <c r="B168" t="n">
-        <v>93197</v>
+        <v>93209</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19840,21 +19841,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19864,10 +19865,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>691007</v>
+        <v>690733</v>
       </c>
       <c r="R168" t="n">
-        <v>7401047</v>
+        <v>7400794</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19899,7 +19900,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19909,7 +19910,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19939,38 +19940,38 @@
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960661</t>
+          <t>https://artportalen.se/Sighting/128960416</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128960416</v>
+        <v>128960677</v>
       </c>
       <c r="B169" t="n">
-        <v>93209</v>
+        <v>89143</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4366</v>
+        <v>4405</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19980,10 +19981,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>690733</v>
+        <v>691492</v>
       </c>
       <c r="R169" t="n">
-        <v>7400794</v>
+        <v>7400692</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20010,22 +20011,22 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20055,51 +20056,51 @@
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960416</t>
+          <t>https://artportalen.se/Sighting/128960677</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128960677</v>
+        <v>128146051</v>
       </c>
       <c r="B170" t="n">
-        <v>89143</v>
+        <v>92841</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4405</v>
+        <v>4745</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>691492</v>
+        <v>691386</v>
       </c>
       <c r="R170" t="n">
-        <v>7400692</v>
+        <v>7400998</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20126,22 +20127,22 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20156,28 +20157,24 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960677</t>
+          <t>https://artportalen.se/Sighting/128146051</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128146051</v>
+        <v>128960394</v>
       </c>
       <c r="B171" t="n">
         <v>92841</v>
@@ -20208,14 +20205,14 @@
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>691386</v>
+        <v>691657</v>
       </c>
       <c r="R171" t="n">
-        <v>7400998</v>
+        <v>7400847</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20242,22 +20239,22 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20272,24 +20269,28 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY171" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146051</t>
+          <t>https://artportalen.se/Sighting/128960394</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128960394</v>
+        <v>128960396</v>
       </c>
       <c r="B172" t="n">
         <v>92841</v>
@@ -20324,10 +20325,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>691657</v>
+        <v>691486</v>
       </c>
       <c r="R172" t="n">
-        <v>7400847</v>
+        <v>7400758</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20359,7 +20360,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -20369,7 +20370,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20399,13 +20400,13 @@
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960394</t>
+          <t>https://artportalen.se/Sighting/128960396</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128960396</v>
+        <v>128960397</v>
       </c>
       <c r="B173" t="n">
         <v>92841</v>
@@ -20440,10 +20441,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>691486</v>
+        <v>690679</v>
       </c>
       <c r="R173" t="n">
-        <v>7400758</v>
+        <v>7400680</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20470,22 +20471,22 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20515,13 +20516,13 @@
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960396</t>
+          <t>https://artportalen.se/Sighting/128960397</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128960397</v>
+        <v>128960398</v>
       </c>
       <c r="B174" t="n">
         <v>92841</v>
@@ -20556,10 +20557,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>690679</v>
+        <v>690713</v>
       </c>
       <c r="R174" t="n">
-        <v>7400680</v>
+        <v>7400706</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20591,7 +20592,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -20601,7 +20602,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20631,13 +20632,13 @@
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960397</t>
+          <t>https://artportalen.se/Sighting/128960398</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128960398</v>
+        <v>128960399</v>
       </c>
       <c r="B175" t="n">
         <v>92841</v>
@@ -20672,10 +20673,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>690713</v>
+        <v>690819</v>
       </c>
       <c r="R175" t="n">
-        <v>7400706</v>
+        <v>7400882</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20707,7 +20708,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -20717,7 +20718,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20747,16 +20748,16 @@
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960398</t>
+          <t>https://artportalen.se/Sighting/128960399</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128960399</v>
+        <v>128960436</v>
       </c>
       <c r="B176" t="n">
-        <v>92841</v>
+        <v>90522</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20764,21 +20765,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4745</v>
+        <v>4962</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -20788,10 +20789,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>690819</v>
+        <v>691019</v>
       </c>
       <c r="R176" t="n">
-        <v>7400882</v>
+        <v>7400845</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20818,22 +20819,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20863,13 +20864,13 @@
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960399</t>
+          <t>https://artportalen.se/Sighting/128960436</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128960436</v>
+        <v>128960437</v>
       </c>
       <c r="B177" t="n">
         <v>90522</v>
@@ -20904,10 +20905,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>691019</v>
+        <v>691225</v>
       </c>
       <c r="R177" t="n">
-        <v>7400845</v>
+        <v>7400593</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20939,7 +20940,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20949,7 +20950,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20979,13 +20980,13 @@
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960436</t>
+          <t>https://artportalen.se/Sighting/128960437</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128960437</v>
+        <v>128960439</v>
       </c>
       <c r="B178" t="n">
         <v>90522</v>
@@ -21020,10 +21021,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>691225</v>
+        <v>690708</v>
       </c>
       <c r="R178" t="n">
-        <v>7400593</v>
+        <v>7400815</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21050,22 +21051,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21095,38 +21096,38 @@
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960437</t>
+          <t>https://artportalen.se/Sighting/128960439</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128960439</v>
+        <v>128960356</v>
       </c>
       <c r="B179" t="n">
-        <v>90522</v>
+        <v>91872</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4962</v>
+        <v>5447</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21136,10 +21137,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>690708</v>
+        <v>691028</v>
       </c>
       <c r="R179" t="n">
-        <v>7400815</v>
+        <v>7400838</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21166,22 +21167,22 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21211,38 +21212,38 @@
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960439</t>
+          <t>https://artportalen.se/Sighting/128960356</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128960356</v>
+        <v>128960402</v>
       </c>
       <c r="B180" t="n">
-        <v>91872</v>
+        <v>93223</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -21252,10 +21253,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>691028</v>
+        <v>690717</v>
       </c>
       <c r="R180" t="n">
-        <v>7400838</v>
+        <v>7400812</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -21282,22 +21283,22 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21327,16 +21328,16 @@
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960356</t>
+          <t>https://artportalen.se/Sighting/128960402</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128960402</v>
+        <v>128960550</v>
       </c>
       <c r="B181" t="n">
-        <v>93223</v>
+        <v>92556</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21344,21 +21345,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5448</v>
+        <v>5454</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -21368,10 +21369,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>690717</v>
+        <v>691708</v>
       </c>
       <c r="R181" t="n">
-        <v>7400812</v>
+        <v>7401045</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21398,22 +21399,22 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21443,16 +21444,16 @@
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960402</t>
+          <t>https://artportalen.se/Sighting/128960550</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128960550</v>
+        <v>128144838</v>
       </c>
       <c r="B182" t="n">
-        <v>92556</v>
+        <v>78730</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21460,34 +21461,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5454</v>
+        <v>6437</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>691708</v>
+        <v>691841</v>
       </c>
       <c r="R182" t="n">
-        <v>7401045</v>
+        <v>7400785</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21514,22 +21515,22 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21544,28 +21545,24 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY182" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960550</t>
+          <t>https://artportalen.se/Sighting/128144838</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128144838</v>
+        <v>128144839</v>
       </c>
       <c r="B183" t="n">
         <v>78730</v>
@@ -21600,10 +21597,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>691841</v>
+        <v>691806</v>
       </c>
       <c r="R183" t="n">
-        <v>7400785</v>
+        <v>7400707</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21635,7 +21632,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -21645,7 +21642,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21671,13 +21668,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144838</t>
+          <t>https://artportalen.se/Sighting/128144839</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128144839</v>
+        <v>128144840</v>
       </c>
       <c r="B184" t="n">
         <v>78730</v>
@@ -21712,10 +21709,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>691806</v>
+        <v>691520</v>
       </c>
       <c r="R184" t="n">
-        <v>7400707</v>
+        <v>7400858</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21747,7 +21744,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -21757,7 +21754,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21783,13 +21780,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144839</t>
+          <t>https://artportalen.se/Sighting/128144840</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128144840</v>
+        <v>128146075</v>
       </c>
       <c r="B185" t="n">
         <v>78730</v>
@@ -21824,10 +21821,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>691520</v>
+        <v>691077</v>
       </c>
       <c r="R185" t="n">
-        <v>7400858</v>
+        <v>7400880</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21859,7 +21856,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21869,7 +21866,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21895,13 +21892,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144840</t>
+          <t>https://artportalen.se/Sighting/128146075</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128146075</v>
+        <v>128960690</v>
       </c>
       <c r="B186" t="n">
         <v>78730</v>
@@ -21932,14 +21929,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>691077</v>
+        <v>690817</v>
       </c>
       <c r="R186" t="n">
-        <v>7400880</v>
+        <v>7400668</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21966,22 +21963,22 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21996,24 +21993,28 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY186" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146075</t>
+          <t>https://artportalen.se/Sighting/128960690</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128960690</v>
+        <v>128960693</v>
       </c>
       <c r="B187" t="n">
         <v>78730</v>
@@ -22048,10 +22049,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>690817</v>
+        <v>691595</v>
       </c>
       <c r="R187" t="n">
-        <v>7400668</v>
+        <v>7401115</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -22078,22 +22079,22 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -22123,16 +22124,16 @@
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960690</t>
+          <t>https://artportalen.se/Sighting/128960693</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128960693</v>
+        <v>128144829</v>
       </c>
       <c r="B188" t="n">
-        <v>78730</v>
+        <v>79084</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22140,34 +22141,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>691595</v>
+        <v>691811</v>
       </c>
       <c r="R188" t="n">
-        <v>7401115</v>
+        <v>7400740</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -22194,22 +22195,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -22224,31 +22225,27 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY188" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960693</t>
+          <t>https://artportalen.se/Sighting/128144829</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128144829</v>
+        <v>128144819</v>
       </c>
       <c r="B189" t="n">
-        <v>79084</v>
+        <v>79946</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22256,21 +22253,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -22280,10 +22277,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>691811</v>
+        <v>691675</v>
       </c>
       <c r="R189" t="n">
-        <v>7400740</v>
+        <v>7401012</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22315,7 +22312,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -22325,7 +22322,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -22351,13 +22348,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144829</t>
+          <t>https://artportalen.se/Sighting/128144819</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128144819</v>
+        <v>128144820</v>
       </c>
       <c r="B190" t="n">
         <v>79946</v>
@@ -22392,10 +22389,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>691675</v>
+        <v>691749</v>
       </c>
       <c r="R190" t="n">
-        <v>7401012</v>
+        <v>7400999</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -22427,7 +22424,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -22437,7 +22434,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22463,13 +22460,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144819</t>
+          <t>https://artportalen.se/Sighting/128144820</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128144820</v>
+        <v>128144822</v>
       </c>
       <c r="B191" t="n">
         <v>79946</v>
@@ -22504,10 +22501,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>691749</v>
+        <v>691662</v>
       </c>
       <c r="R191" t="n">
-        <v>7400999</v>
+        <v>7400760</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22539,7 +22536,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -22549,7 +22546,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22575,13 +22572,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144820</t>
+          <t>https://artportalen.se/Sighting/128144822</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128144822</v>
+        <v>128144823</v>
       </c>
       <c r="B192" t="n">
         <v>79946</v>
@@ -22616,10 +22613,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>691662</v>
+        <v>691519</v>
       </c>
       <c r="R192" t="n">
-        <v>7400760</v>
+        <v>7400859</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22651,7 +22648,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -22661,7 +22658,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22687,13 +22684,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144822</t>
+          <t>https://artportalen.se/Sighting/128144823</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128144823</v>
+        <v>128146042</v>
       </c>
       <c r="B193" t="n">
         <v>79946</v>
@@ -22728,10 +22725,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>691519</v>
+        <v>691337</v>
       </c>
       <c r="R193" t="n">
-        <v>7400859</v>
+        <v>7400753</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22763,7 +22760,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -22773,7 +22770,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22799,13 +22796,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144823</t>
+          <t>https://artportalen.se/Sighting/128146042</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128146042</v>
+        <v>128960357</v>
       </c>
       <c r="B194" t="n">
         <v>79946</v>
@@ -22836,14 +22833,14 @@
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>691337</v>
+        <v>691748</v>
       </c>
       <c r="R194" t="n">
-        <v>7400753</v>
+        <v>7400820</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22870,22 +22867,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22900,24 +22897,28 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY194" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146042</t>
+          <t>https://artportalen.se/Sighting/128960357</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128960357</v>
+        <v>128960358</v>
       </c>
       <c r="B195" t="n">
         <v>79946</v>
@@ -22952,10 +22953,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>691748</v>
+        <v>691772</v>
       </c>
       <c r="R195" t="n">
-        <v>7400820</v>
+        <v>7400877</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22987,7 +22988,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22997,7 +22998,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -23027,13 +23028,13 @@
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960357</t>
+          <t>https://artportalen.se/Sighting/128960358</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128960358</v>
+        <v>128960359</v>
       </c>
       <c r="B196" t="n">
         <v>79946</v>
@@ -23068,10 +23069,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>691772</v>
+        <v>691774</v>
       </c>
       <c r="R196" t="n">
-        <v>7400877</v>
+        <v>7401018</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -23103,7 +23104,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -23113,7 +23114,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -23143,51 +23144,51 @@
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960358</t>
+          <t>https://artportalen.se/Sighting/128960359</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128960359</v>
+        <v>128144824</v>
       </c>
       <c r="B197" t="n">
-        <v>79946</v>
+        <v>80336</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>691774</v>
+        <v>691607</v>
       </c>
       <c r="R197" t="n">
-        <v>7401018</v>
+        <v>7400989</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23214,22 +23215,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -23244,28 +23245,24 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY197" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960359</t>
+          <t>https://artportalen.se/Sighting/128144824</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128144824</v>
+        <v>128144825</v>
       </c>
       <c r="B198" t="n">
         <v>80336</v>
@@ -23300,10 +23297,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>691607</v>
+        <v>691427</v>
       </c>
       <c r="R198" t="n">
-        <v>7400989</v>
+        <v>7401053</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23335,7 +23332,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -23345,7 +23342,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23371,38 +23368,38 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144824</t>
+          <t>https://artportalen.se/Sighting/128144825</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128144825</v>
+        <v>128146058</v>
       </c>
       <c r="B199" t="n">
-        <v>80336</v>
+        <v>80432</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -23412,10 +23409,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>691427</v>
+        <v>691437</v>
       </c>
       <c r="R199" t="n">
-        <v>7401053</v>
+        <v>7401034</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -23447,7 +23444,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -23457,7 +23454,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -23483,51 +23480,51 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144825</t>
+          <t>https://artportalen.se/Sighting/128146058</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128146058</v>
+        <v>128960405</v>
       </c>
       <c r="B200" t="n">
-        <v>80432</v>
+        <v>80461</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>691437</v>
+        <v>690835</v>
       </c>
       <c r="R200" t="n">
-        <v>7401034</v>
+        <v>7400894</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -23554,22 +23551,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23584,24 +23581,28 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY200" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146058</t>
+          <t>https://artportalen.se/Sighting/128960405</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128960405</v>
+        <v>128960406</v>
       </c>
       <c r="B201" t="n">
         <v>80461</v>
@@ -23636,10 +23637,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>690835</v>
+        <v>691215</v>
       </c>
       <c r="R201" t="n">
-        <v>7400894</v>
+        <v>7400790</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23666,22 +23667,22 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23711,13 +23712,13 @@
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960405</t>
+          <t>https://artportalen.se/Sighting/128960406</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128960406</v>
+        <v>128960407</v>
       </c>
       <c r="B202" t="n">
         <v>80461</v>
@@ -23752,10 +23753,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>691215</v>
+        <v>691472</v>
       </c>
       <c r="R202" t="n">
-        <v>7400790</v>
+        <v>7401056</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23787,7 +23788,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -23797,7 +23798,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23827,16 +23828,16 @@
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960406</t>
+          <t>https://artportalen.se/Sighting/128960407</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128960407</v>
+        <v>128960683</v>
       </c>
       <c r="B203" t="n">
-        <v>80461</v>
+        <v>80467</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23844,21 +23845,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23868,10 +23869,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>691472</v>
+        <v>690835</v>
       </c>
       <c r="R203" t="n">
-        <v>7401056</v>
+        <v>7400892</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23898,22 +23899,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23943,51 +23944,51 @@
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960407</t>
+          <t>https://artportalen.se/Sighting/128960683</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128960683</v>
+        <v>128146073</v>
       </c>
       <c r="B204" t="n">
-        <v>80467</v>
+        <v>78334</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6463</v>
+        <v>6487</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>690835</v>
+        <v>691079</v>
       </c>
       <c r="R204" t="n">
-        <v>7400892</v>
+        <v>7400877</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -24014,22 +24015,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -24044,28 +24045,24 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY204" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960683</t>
+          <t>https://artportalen.se/Sighting/128146073</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128146073</v>
+        <v>128960684</v>
       </c>
       <c r="B205" t="n">
         <v>78334</v>
@@ -24096,14 +24093,14 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>691079</v>
+        <v>691442</v>
       </c>
       <c r="R205" t="n">
-        <v>7400877</v>
+        <v>7400932</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -24130,22 +24127,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24160,24 +24157,28 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY205" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146073</t>
+          <t>https://artportalen.se/Sighting/128960684</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128960684</v>
+        <v>128960685</v>
       </c>
       <c r="B206" t="n">
         <v>78334</v>
@@ -24212,10 +24213,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>691442</v>
+        <v>690998</v>
       </c>
       <c r="R206" t="n">
-        <v>7400932</v>
+        <v>7401040</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24242,22 +24243,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24287,13 +24288,13 @@
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960684</t>
+          <t>https://artportalen.se/Sighting/128960685</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128960685</v>
+        <v>128960687</v>
       </c>
       <c r="B207" t="n">
         <v>78334</v>
@@ -24328,10 +24329,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>690998</v>
+        <v>691772</v>
       </c>
       <c r="R207" t="n">
-        <v>7401040</v>
+        <v>7401045</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24358,22 +24359,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24403,16 +24404,16 @@
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960685</t>
+          <t>https://artportalen.se/Sighting/128960687</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128960687</v>
+        <v>128144826</v>
       </c>
       <c r="B208" t="n">
-        <v>78334</v>
+        <v>5495</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24420,34 +24421,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6487</v>
+        <v>101410</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>691772</v>
+        <v>691845</v>
       </c>
       <c r="R208" t="n">
-        <v>7401045</v>
+        <v>7400932</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24474,22 +24475,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24504,53 +24505,49 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY208" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960687</t>
+          <t>https://artportalen.se/Sighting/128144826</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128144826</v>
+        <v>128144830</v>
       </c>
       <c r="B209" t="n">
-        <v>5495</v>
+        <v>99118</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -24560,10 +24557,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>691845</v>
+        <v>691395</v>
       </c>
       <c r="R209" t="n">
-        <v>7400932</v>
+        <v>7401068</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -24595,7 +24592,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -24605,7 +24602,12 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24631,13 +24633,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144826</t>
+          <t>https://artportalen.se/Sighting/128144830</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128144830</v>
+        <v>128144833</v>
       </c>
       <c r="B210" t="n">
         <v>99118</v>
@@ -24672,10 +24674,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>691395</v>
+        <v>691471</v>
       </c>
       <c r="R210" t="n">
-        <v>7401068</v>
+        <v>7401138</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -24707,7 +24709,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -24717,12 +24719,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24748,13 +24745,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144830</t>
+          <t>https://artportalen.se/Sighting/128144833</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128144833</v>
+        <v>128146060</v>
       </c>
       <c r="B211" t="n">
         <v>99118</v>
@@ -24789,10 +24786,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>691471</v>
+        <v>691443</v>
       </c>
       <c r="R211" t="n">
-        <v>7401138</v>
+        <v>7401033</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -24824,7 +24821,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -24834,7 +24831,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24860,13 +24857,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144833</t>
+          <t>https://artportalen.se/Sighting/128146060</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128146060</v>
+        <v>128960451</v>
       </c>
       <c r="B212" t="n">
         <v>99118</v>
@@ -24897,14 +24894,14 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>691443</v>
+        <v>691520</v>
       </c>
       <c r="R212" t="n">
-        <v>7401033</v>
+        <v>7401010</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24931,22 +24928,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24961,24 +24958,28 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY212" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146060</t>
+          <t>https://artportalen.se/Sighting/128960451</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128960451</v>
+        <v>128960455</v>
       </c>
       <c r="B213" t="n">
         <v>99118</v>
@@ -25013,10 +25014,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>691520</v>
+        <v>691615</v>
       </c>
       <c r="R213" t="n">
-        <v>7401010</v>
+        <v>7400959</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25048,7 +25049,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -25058,7 +25059,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -25088,13 +25089,13 @@
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960451</t>
+          <t>https://artportalen.se/Sighting/128960455</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128960455</v>
+        <v>128960456</v>
       </c>
       <c r="B214" t="n">
         <v>99118</v>
@@ -25129,10 +25130,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>691615</v>
+        <v>691641</v>
       </c>
       <c r="R214" t="n">
-        <v>7400959</v>
+        <v>7400939</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25164,7 +25165,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -25174,7 +25175,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -25204,13 +25205,13 @@
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960455</t>
+          <t>https://artportalen.se/Sighting/128960456</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128960456</v>
+        <v>128960459</v>
       </c>
       <c r="B215" t="n">
         <v>99118</v>
@@ -25245,10 +25246,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>691641</v>
+        <v>691498</v>
       </c>
       <c r="R215" t="n">
-        <v>7400939</v>
+        <v>7401073</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25280,7 +25281,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -25290,7 +25291,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -25320,13 +25321,13 @@
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960456</t>
+          <t>https://artportalen.se/Sighting/128960459</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128960459</v>
+        <v>128960460</v>
       </c>
       <c r="B216" t="n">
         <v>99118</v>
@@ -25361,10 +25362,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>691498</v>
+        <v>691513</v>
       </c>
       <c r="R216" t="n">
-        <v>7401073</v>
+        <v>7401038</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25396,7 +25397,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -25406,7 +25407,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -25436,13 +25437,13 @@
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960459</t>
+          <t>https://artportalen.se/Sighting/128960460</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128960460</v>
+        <v>128960461</v>
       </c>
       <c r="B217" t="n">
         <v>99118</v>
@@ -25477,10 +25478,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>691513</v>
+        <v>691285</v>
       </c>
       <c r="R217" t="n">
-        <v>7401038</v>
+        <v>7400841</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25512,7 +25513,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -25522,7 +25523,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25552,13 +25553,13 @@
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960460</t>
+          <t>https://artportalen.se/Sighting/128960461</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128960461</v>
+        <v>128960463</v>
       </c>
       <c r="B218" t="n">
         <v>99118</v>
@@ -25593,10 +25594,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>691285</v>
+        <v>691259</v>
       </c>
       <c r="R218" t="n">
-        <v>7400841</v>
+        <v>7400802</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -25628,7 +25629,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -25638,7 +25639,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25668,13 +25669,13 @@
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960461</t>
+          <t>https://artportalen.se/Sighting/128960463</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128960463</v>
+        <v>128960464</v>
       </c>
       <c r="B219" t="n">
         <v>99118</v>
@@ -25709,10 +25710,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>691259</v>
+        <v>691251</v>
       </c>
       <c r="R219" t="n">
-        <v>7400802</v>
+        <v>7400808</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25744,7 +25745,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -25754,7 +25755,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -25784,13 +25785,13 @@
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960463</t>
+          <t>https://artportalen.se/Sighting/128960464</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128960464</v>
+        <v>128960465</v>
       </c>
       <c r="B220" t="n">
         <v>99118</v>
@@ -25825,10 +25826,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>691251</v>
+        <v>691184</v>
       </c>
       <c r="R220" t="n">
-        <v>7400808</v>
+        <v>7400869</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25860,7 +25861,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -25870,7 +25871,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -25900,13 +25901,13 @@
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960464</t>
+          <t>https://artportalen.se/Sighting/128960465</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128960465</v>
+        <v>128960467</v>
       </c>
       <c r="B221" t="n">
         <v>99118</v>
@@ -25941,10 +25942,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>691184</v>
+        <v>691182</v>
       </c>
       <c r="R221" t="n">
-        <v>7400869</v>
+        <v>7400878</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26016,13 +26017,13 @@
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960465</t>
+          <t>https://artportalen.se/Sighting/128960467</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128960467</v>
+        <v>128960468</v>
       </c>
       <c r="B222" t="n">
         <v>99118</v>
@@ -26057,10 +26058,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>691182</v>
+        <v>691175</v>
       </c>
       <c r="R222" t="n">
-        <v>7400878</v>
+        <v>7400884</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26092,7 +26093,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -26102,7 +26103,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -26132,13 +26133,13 @@
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960467</t>
+          <t>https://artportalen.se/Sighting/128960468</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128960468</v>
+        <v>128960469</v>
       </c>
       <c r="B223" t="n">
         <v>99118</v>
@@ -26173,10 +26174,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>691175</v>
+        <v>691149</v>
       </c>
       <c r="R223" t="n">
-        <v>7400884</v>
+        <v>7400912</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26208,7 +26209,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -26218,7 +26219,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -26248,13 +26249,13 @@
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960468</t>
+          <t>https://artportalen.se/Sighting/128960469</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128960469</v>
+        <v>128960470</v>
       </c>
       <c r="B224" t="n">
         <v>99118</v>
@@ -26289,10 +26290,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>691149</v>
+        <v>691148</v>
       </c>
       <c r="R224" t="n">
-        <v>7400912</v>
+        <v>7400926</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26324,7 +26325,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -26334,7 +26335,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26364,13 +26365,13 @@
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960469</t>
+          <t>https://artportalen.se/Sighting/128960470</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128960470</v>
+        <v>128960471</v>
       </c>
       <c r="B225" t="n">
         <v>99118</v>
@@ -26405,10 +26406,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>691148</v>
+        <v>691137</v>
       </c>
       <c r="R225" t="n">
-        <v>7400926</v>
+        <v>7400938</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26480,13 +26481,13 @@
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960470</t>
+          <t>https://artportalen.se/Sighting/128960471</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128960471</v>
+        <v>128960472</v>
       </c>
       <c r="B226" t="n">
         <v>99118</v>
@@ -26521,10 +26522,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>691137</v>
+        <v>690998</v>
       </c>
       <c r="R226" t="n">
-        <v>7400938</v>
+        <v>7400789</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26556,7 +26557,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -26566,7 +26567,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -26596,13 +26597,13 @@
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960471</t>
+          <t>https://artportalen.se/Sighting/128960472</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128960472</v>
+        <v>128960473</v>
       </c>
       <c r="B227" t="n">
         <v>99118</v>
@@ -26640,7 +26641,7 @@
         <v>690998</v>
       </c>
       <c r="R227" t="n">
-        <v>7400789</v>
+        <v>7400742</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26672,7 +26673,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -26682,7 +26683,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -26712,13 +26713,13 @@
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960472</t>
+          <t>https://artportalen.se/Sighting/128960473</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128960473</v>
+        <v>128960474</v>
       </c>
       <c r="B228" t="n">
         <v>99118</v>
@@ -26753,10 +26754,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>690998</v>
+        <v>691032</v>
       </c>
       <c r="R228" t="n">
-        <v>7400742</v>
+        <v>7400748</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26788,7 +26789,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -26798,7 +26799,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26828,13 +26829,13 @@
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960473</t>
+          <t>https://artportalen.se/Sighting/128960474</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128960474</v>
+        <v>128960475</v>
       </c>
       <c r="B229" t="n">
         <v>99118</v>
@@ -26869,10 +26870,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>691032</v>
+        <v>691050</v>
       </c>
       <c r="R229" t="n">
-        <v>7400748</v>
+        <v>7400705</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26904,7 +26905,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -26914,7 +26915,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26944,13 +26945,13 @@
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960474</t>
+          <t>https://artportalen.se/Sighting/128960475</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128960475</v>
+        <v>128960476</v>
       </c>
       <c r="B230" t="n">
         <v>99118</v>
@@ -26985,10 +26986,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>691050</v>
+        <v>691094</v>
       </c>
       <c r="R230" t="n">
-        <v>7400705</v>
+        <v>7400693</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27020,7 +27021,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -27030,7 +27031,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -27060,13 +27061,13 @@
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960475</t>
+          <t>https://artportalen.se/Sighting/128960476</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128960476</v>
+        <v>128960477</v>
       </c>
       <c r="B231" t="n">
         <v>99118</v>
@@ -27101,10 +27102,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>691094</v>
+        <v>691104</v>
       </c>
       <c r="R231" t="n">
-        <v>7400693</v>
+        <v>7400683</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -27136,7 +27137,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -27146,7 +27147,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -27176,13 +27177,13 @@
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960476</t>
+          <t>https://artportalen.se/Sighting/128960477</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128960477</v>
+        <v>128960478</v>
       </c>
       <c r="B232" t="n">
         <v>99118</v>
@@ -27217,10 +27218,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>691104</v>
+        <v>691303</v>
       </c>
       <c r="R232" t="n">
-        <v>7400683</v>
+        <v>7400537</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27252,7 +27253,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -27262,7 +27263,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -27292,13 +27293,13 @@
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960477</t>
+          <t>https://artportalen.se/Sighting/128960478</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128960478</v>
+        <v>128960479</v>
       </c>
       <c r="B233" t="n">
         <v>99118</v>
@@ -27333,10 +27334,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>691303</v>
+        <v>691286</v>
       </c>
       <c r="R233" t="n">
-        <v>7400537</v>
+        <v>7400554</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27368,7 +27369,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -27378,7 +27379,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27408,13 +27409,13 @@
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960478</t>
+          <t>https://artportalen.se/Sighting/128960479</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128960479</v>
+        <v>128960480</v>
       </c>
       <c r="B234" t="n">
         <v>99118</v>
@@ -27449,10 +27450,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>691286</v>
+        <v>691030</v>
       </c>
       <c r="R234" t="n">
-        <v>7400554</v>
+        <v>7400688</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27484,7 +27485,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -27494,7 +27495,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -27524,13 +27525,13 @@
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960479</t>
+          <t>https://artportalen.se/Sighting/128960480</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128960480</v>
+        <v>128960481</v>
       </c>
       <c r="B235" t="n">
         <v>99118</v>
@@ -27565,10 +27566,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>691030</v>
+        <v>691054</v>
       </c>
       <c r="R235" t="n">
-        <v>7400688</v>
+        <v>7400678</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27640,13 +27641,13 @@
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960480</t>
+          <t>https://artportalen.se/Sighting/128960481</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128960481</v>
+        <v>128960483</v>
       </c>
       <c r="B236" t="n">
         <v>99118</v>
@@ -27681,10 +27682,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>691054</v>
+        <v>691042</v>
       </c>
       <c r="R236" t="n">
-        <v>7400678</v>
+        <v>7400691</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27716,7 +27717,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -27726,7 +27727,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -27756,13 +27757,13 @@
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960481</t>
+          <t>https://artportalen.se/Sighting/128960483</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128960483</v>
+        <v>128960484</v>
       </c>
       <c r="B237" t="n">
         <v>99118</v>
@@ -27797,10 +27798,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>691042</v>
+        <v>691205</v>
       </c>
       <c r="R237" t="n">
-        <v>7400691</v>
+        <v>7400756</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27832,7 +27833,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27842,7 +27843,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27872,13 +27873,13 @@
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960483</t>
+          <t>https://artportalen.se/Sighting/128960484</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128960484</v>
+        <v>128960485</v>
       </c>
       <c r="B238" t="n">
         <v>99118</v>
@@ -27913,10 +27914,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>691205</v>
+        <v>691491</v>
       </c>
       <c r="R238" t="n">
-        <v>7400756</v>
+        <v>7400689</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27948,7 +27949,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27958,7 +27959,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27988,13 +27989,13 @@
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960484</t>
+          <t>https://artportalen.se/Sighting/128960485</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128960485</v>
+        <v>128960486</v>
       </c>
       <c r="B239" t="n">
         <v>99118</v>
@@ -28029,10 +28030,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>691491</v>
+        <v>691497</v>
       </c>
       <c r="R239" t="n">
-        <v>7400689</v>
+        <v>7400703</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -28064,7 +28065,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -28074,7 +28075,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -28104,13 +28105,13 @@
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960485</t>
+          <t>https://artportalen.se/Sighting/128960486</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128960486</v>
+        <v>128960487</v>
       </c>
       <c r="B240" t="n">
         <v>99118</v>
@@ -28145,10 +28146,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>691497</v>
+        <v>691504</v>
       </c>
       <c r="R240" t="n">
-        <v>7400703</v>
+        <v>7400725</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -28180,7 +28181,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -28190,7 +28191,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -28220,13 +28221,13 @@
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960486</t>
+          <t>https://artportalen.se/Sighting/128960487</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128960487</v>
+        <v>128960488</v>
       </c>
       <c r="B241" t="n">
         <v>99118</v>
@@ -28261,10 +28262,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>691504</v>
+        <v>691464</v>
       </c>
       <c r="R241" t="n">
-        <v>7400725</v>
+        <v>7400741</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -28296,7 +28297,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -28306,7 +28307,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -28336,13 +28337,13 @@
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960487</t>
+          <t>https://artportalen.se/Sighting/128960488</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128960488</v>
+        <v>128960489</v>
       </c>
       <c r="B242" t="n">
         <v>99118</v>
@@ -28377,10 +28378,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>691464</v>
+        <v>691434</v>
       </c>
       <c r="R242" t="n">
-        <v>7400741</v>
+        <v>7400760</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28412,7 +28413,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -28422,7 +28423,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28452,13 +28453,13 @@
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960488</t>
+          <t>https://artportalen.se/Sighting/128960489</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128960489</v>
+        <v>128960491</v>
       </c>
       <c r="B243" t="n">
         <v>99118</v>
@@ -28493,10 +28494,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>691434</v>
+        <v>691488</v>
       </c>
       <c r="R243" t="n">
-        <v>7400760</v>
+        <v>7401047</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28528,7 +28529,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -28538,7 +28539,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -28568,13 +28569,13 @@
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960489</t>
+          <t>https://artportalen.se/Sighting/128960491</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128960491</v>
+        <v>128960492</v>
       </c>
       <c r="B244" t="n">
         <v>99118</v>
@@ -28609,10 +28610,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>691488</v>
+        <v>691483</v>
       </c>
       <c r="R244" t="n">
-        <v>7401047</v>
+        <v>7401061</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28644,7 +28645,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -28654,7 +28655,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -28684,13 +28685,13 @@
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960491</t>
+          <t>https://artportalen.se/Sighting/128960492</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128960492</v>
+        <v>128960493</v>
       </c>
       <c r="B245" t="n">
         <v>99118</v>
@@ -28728,7 +28729,7 @@
         <v>691483</v>
       </c>
       <c r="R245" t="n">
-        <v>7401061</v>
+        <v>7401085</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28760,7 +28761,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -28770,7 +28771,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28800,13 +28801,13 @@
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960492</t>
+          <t>https://artportalen.se/Sighting/128960493</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128960493</v>
+        <v>128960495</v>
       </c>
       <c r="B246" t="n">
         <v>99118</v>
@@ -28841,10 +28842,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>691483</v>
+        <v>691488</v>
       </c>
       <c r="R246" t="n">
-        <v>7401085</v>
+        <v>7401092</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28876,7 +28877,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28886,7 +28887,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28916,13 +28917,13 @@
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960493</t>
+          <t>https://artportalen.se/Sighting/128960495</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128960495</v>
+        <v>128960496</v>
       </c>
       <c r="B247" t="n">
         <v>99118</v>
@@ -28957,10 +28958,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>691488</v>
+        <v>691471</v>
       </c>
       <c r="R247" t="n">
-        <v>7401092</v>
+        <v>7401095</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28992,7 +28993,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -29002,7 +29003,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -29032,13 +29033,13 @@
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960495</t>
+          <t>https://artportalen.se/Sighting/128960496</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128960496</v>
+        <v>128960497</v>
       </c>
       <c r="B248" t="n">
         <v>99118</v>
@@ -29073,10 +29074,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>691471</v>
+        <v>691469</v>
       </c>
       <c r="R248" t="n">
-        <v>7401095</v>
+        <v>7401129</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -29108,7 +29109,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -29118,7 +29119,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -29148,13 +29149,13 @@
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960496</t>
+          <t>https://artportalen.se/Sighting/128960497</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128960497</v>
+        <v>128960503</v>
       </c>
       <c r="B249" t="n">
         <v>99118</v>
@@ -29189,10 +29190,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>691469</v>
+        <v>690957</v>
       </c>
       <c r="R249" t="n">
-        <v>7401129</v>
+        <v>7400856</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -29219,22 +29220,22 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -29264,13 +29265,13 @@
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960497</t>
+          <t>https://artportalen.se/Sighting/128960503</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128960503</v>
+        <v>128960504</v>
       </c>
       <c r="B250" t="n">
         <v>99118</v>
@@ -29305,10 +29306,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>690957</v>
+        <v>690949</v>
       </c>
       <c r="R250" t="n">
-        <v>7400856</v>
+        <v>7400850</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29340,7 +29341,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -29350,7 +29351,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29380,13 +29381,13 @@
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960503</t>
+          <t>https://artportalen.se/Sighting/128960504</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128960504</v>
+        <v>128960505</v>
       </c>
       <c r="B251" t="n">
         <v>99118</v>
@@ -29421,10 +29422,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>690949</v>
+        <v>690992</v>
       </c>
       <c r="R251" t="n">
-        <v>7400850</v>
+        <v>7400806</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29456,7 +29457,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -29466,7 +29467,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29496,13 +29497,13 @@
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960504</t>
+          <t>https://artportalen.se/Sighting/128960505</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128960505</v>
+        <v>128960506</v>
       </c>
       <c r="B252" t="n">
         <v>99118</v>
@@ -29537,10 +29538,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>690992</v>
+        <v>690964</v>
       </c>
       <c r="R252" t="n">
-        <v>7400806</v>
+        <v>7400788</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29572,7 +29573,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -29582,7 +29583,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29612,13 +29613,13 @@
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960505</t>
+          <t>https://artportalen.se/Sighting/128960506</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128960506</v>
+        <v>128960507</v>
       </c>
       <c r="B253" t="n">
         <v>99118</v>
@@ -29653,10 +29654,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>690964</v>
+        <v>690928</v>
       </c>
       <c r="R253" t="n">
-        <v>7400788</v>
+        <v>7400812</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29688,7 +29689,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -29698,7 +29699,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29728,13 +29729,13 @@
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960506</t>
+          <t>https://artportalen.se/Sighting/128960507</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128960507</v>
+        <v>128960508</v>
       </c>
       <c r="B254" t="n">
         <v>99118</v>
@@ -29769,10 +29770,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>690928</v>
+        <v>690820</v>
       </c>
       <c r="R254" t="n">
-        <v>7400812</v>
+        <v>7400917</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29804,7 +29805,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -29814,7 +29815,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29844,13 +29845,13 @@
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960507</t>
+          <t>https://artportalen.se/Sighting/128960508</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128960508</v>
+        <v>128960509</v>
       </c>
       <c r="B255" t="n">
         <v>99118</v>
@@ -29885,10 +29886,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>690820</v>
+        <v>690841</v>
       </c>
       <c r="R255" t="n">
-        <v>7400917</v>
+        <v>7400937</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29920,7 +29921,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -29930,7 +29931,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29960,13 +29961,13 @@
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960508</t>
+          <t>https://artportalen.se/Sighting/128960509</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128960509</v>
+        <v>128960510</v>
       </c>
       <c r="B256" t="n">
         <v>99118</v>
@@ -30001,10 +30002,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>690841</v>
+        <v>690855</v>
       </c>
       <c r="R256" t="n">
-        <v>7400937</v>
+        <v>7400940</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -30036,7 +30037,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -30046,7 +30047,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -30076,13 +30077,13 @@
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960509</t>
+          <t>https://artportalen.se/Sighting/128960510</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128960510</v>
+        <v>128960511</v>
       </c>
       <c r="B257" t="n">
         <v>99118</v>
@@ -30117,10 +30118,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>690855</v>
+        <v>690875</v>
       </c>
       <c r="R257" t="n">
-        <v>7400940</v>
+        <v>7400942</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -30152,7 +30153,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -30162,7 +30163,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -30192,13 +30193,13 @@
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960510</t>
+          <t>https://artportalen.se/Sighting/128960511</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128960511</v>
+        <v>128960512</v>
       </c>
       <c r="B258" t="n">
         <v>99118</v>
@@ -30233,10 +30234,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>690875</v>
+        <v>691026</v>
       </c>
       <c r="R258" t="n">
-        <v>7400942</v>
+        <v>7401085</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -30268,7 +30269,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -30278,7 +30279,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -30308,13 +30309,13 @@
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960511</t>
+          <t>https://artportalen.se/Sighting/128960512</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128960512</v>
+        <v>128960513</v>
       </c>
       <c r="B259" t="n">
         <v>99118</v>
@@ -30349,10 +30350,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>691026</v>
+        <v>691071</v>
       </c>
       <c r="R259" t="n">
-        <v>7401085</v>
+        <v>7401097</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -30384,7 +30385,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -30394,7 +30395,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -30424,13 +30425,13 @@
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960512</t>
+          <t>https://artportalen.se/Sighting/128960513</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128960513</v>
+        <v>128960515</v>
       </c>
       <c r="B260" t="n">
         <v>99118</v>
@@ -30465,10 +30466,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>691071</v>
+        <v>691061</v>
       </c>
       <c r="R260" t="n">
-        <v>7401097</v>
+        <v>7401094</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30500,7 +30501,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -30510,7 +30511,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30540,13 +30541,13 @@
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960513</t>
+          <t>https://artportalen.se/Sighting/128960515</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128960515</v>
+        <v>128960516</v>
       </c>
       <c r="B261" t="n">
         <v>99118</v>
@@ -30581,10 +30582,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>691061</v>
+        <v>691115</v>
       </c>
       <c r="R261" t="n">
-        <v>7401094</v>
+        <v>7401115</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30616,7 +30617,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -30626,7 +30627,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30656,51 +30657,51 @@
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960515</t>
+          <t>https://artportalen.se/Sighting/128960516</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128960516</v>
+        <v>128144827</v>
       </c>
       <c r="B262" t="n">
-        <v>99118</v>
+        <v>79085</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>691115</v>
+        <v>691749</v>
       </c>
       <c r="R262" t="n">
-        <v>7401115</v>
+        <v>7400999</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30727,22 +30728,22 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -30757,28 +30758,24 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY262" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960516</t>
+          <t>https://artportalen.se/Sighting/128144827</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128144827</v>
+        <v>128144828</v>
       </c>
       <c r="B263" t="n">
         <v>79085</v>
@@ -30813,10 +30810,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>691749</v>
+        <v>691820</v>
       </c>
       <c r="R263" t="n">
-        <v>7400999</v>
+        <v>7400729</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30848,7 +30845,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -30858,7 +30855,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -30884,16 +30881,16 @@
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144827</t>
+          <t>https://artportalen.se/Sighting/128144828</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128144828</v>
+        <v>128146043</v>
       </c>
       <c r="B264" t="n">
-        <v>79085</v>
+        <v>79917</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30901,21 +30898,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -30925,10 +30922,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>691820</v>
+        <v>691657</v>
       </c>
       <c r="R264" t="n">
-        <v>7400729</v>
+        <v>7400717</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30960,7 +30957,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -30970,7 +30967,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30996,13 +30993,13 @@
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144828</t>
+          <t>https://artportalen.se/Sighting/128146043</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128146043</v>
+        <v>128146044</v>
       </c>
       <c r="B265" t="n">
         <v>79917</v>
@@ -31037,10 +31034,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>691657</v>
+        <v>691077</v>
       </c>
       <c r="R265" t="n">
-        <v>7400717</v>
+        <v>7400881</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -31072,7 +31069,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -31082,7 +31079,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -31108,13 +31105,13 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146043</t>
+          <t>https://artportalen.se/Sighting/128146044</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128146044</v>
+        <v>128960360</v>
       </c>
       <c r="B266" t="n">
         <v>79917</v>
@@ -31145,14 +31142,14 @@
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>691077</v>
+        <v>691748</v>
       </c>
       <c r="R266" t="n">
-        <v>7400881</v>
+        <v>7400820</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -31179,22 +31176,22 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -31209,24 +31206,28 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY266" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146044</t>
+          <t>https://artportalen.se/Sighting/128960360</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128960360</v>
+        <v>128960361</v>
       </c>
       <c r="B267" t="n">
         <v>79917</v>
@@ -31261,10 +31262,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>691748</v>
+        <v>691629</v>
       </c>
       <c r="R267" t="n">
-        <v>7400820</v>
+        <v>7400883</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -31296,7 +31297,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -31306,7 +31307,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -31336,13 +31337,13 @@
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960360</t>
+          <t>https://artportalen.se/Sighting/128960361</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128960361</v>
+        <v>128960362</v>
       </c>
       <c r="B268" t="n">
         <v>79917</v>
@@ -31377,10 +31378,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>691629</v>
+        <v>691425</v>
       </c>
       <c r="R268" t="n">
-        <v>7400883</v>
+        <v>7400943</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -31412,7 +31413,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -31422,7 +31423,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -31452,13 +31453,13 @@
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960361</t>
+          <t>https://artportalen.se/Sighting/128960362</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128960362</v>
+        <v>128960363</v>
       </c>
       <c r="B269" t="n">
         <v>79917</v>
@@ -31493,10 +31494,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>691425</v>
+        <v>690997</v>
       </c>
       <c r="R269" t="n">
-        <v>7400943</v>
+        <v>7401042</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31523,22 +31524,22 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -31568,13 +31569,13 @@
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960362</t>
+          <t>https://artportalen.se/Sighting/128960363</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128960363</v>
+        <v>128960365</v>
       </c>
       <c r="B270" t="n">
         <v>79917</v>
@@ -31609,10 +31610,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>690997</v>
+        <v>691772</v>
       </c>
       <c r="R270" t="n">
-        <v>7401042</v>
+        <v>7401045</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31639,22 +31640,22 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31684,13 +31685,13 @@
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960363</t>
+          <t>https://artportalen.se/Sighting/128960365</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128960365</v>
+        <v>128960366</v>
       </c>
       <c r="B271" t="n">
         <v>79917</v>
@@ -31725,10 +31726,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>691772</v>
+        <v>691628</v>
       </c>
       <c r="R271" t="n">
-        <v>7401045</v>
+        <v>7401071</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31760,7 +31761,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -31770,7 +31771,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31800,13 +31801,13 @@
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960365</t>
+          <t>https://artportalen.se/Sighting/128960366</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128960366</v>
+        <v>128960368</v>
       </c>
       <c r="B272" t="n">
         <v>79917</v>
@@ -31841,10 +31842,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>691628</v>
+        <v>691561</v>
       </c>
       <c r="R272" t="n">
-        <v>7401071</v>
+        <v>7401113</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -31876,7 +31877,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -31886,7 +31887,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -31916,13 +31917,13 @@
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960366</t>
+          <t>https://artportalen.se/Sighting/128960368</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128960368</v>
+        <v>128960369</v>
       </c>
       <c r="B273" t="n">
         <v>79917</v>
@@ -31957,10 +31958,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>691561</v>
+        <v>691330</v>
       </c>
       <c r="R273" t="n">
-        <v>7401113</v>
+        <v>7400743</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -31992,7 +31993,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -32002,7 +32003,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -32032,13 +32033,13 @@
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960368</t>
+          <t>https://artportalen.se/Sighting/128960369</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128960369</v>
+        <v>128960370</v>
       </c>
       <c r="B274" t="n">
         <v>79917</v>
@@ -32073,10 +32074,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>691330</v>
+        <v>691375</v>
       </c>
       <c r="R274" t="n">
-        <v>7400743</v>
+        <v>7400750</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -32108,7 +32109,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -32118,7 +32119,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -32148,13 +32149,13 @@
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960369</t>
+          <t>https://artportalen.se/Sighting/128960370</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128960370</v>
+        <v>128960371</v>
       </c>
       <c r="B275" t="n">
         <v>79917</v>
@@ -32189,10 +32190,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>691375</v>
+        <v>691493</v>
       </c>
       <c r="R275" t="n">
-        <v>7400750</v>
+        <v>7400837</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -32224,7 +32225,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -32234,7 +32235,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -32264,51 +32265,51 @@
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960370</t>
+          <t>https://artportalen.se/Sighting/128960371</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128960371</v>
+        <v>128146053</v>
       </c>
       <c r="B276" t="n">
-        <v>79917</v>
+        <v>93228</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>229821</v>
+        <v>232140</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>691493</v>
+        <v>691789</v>
       </c>
       <c r="R276" t="n">
-        <v>7400837</v>
+        <v>7400698</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -32335,22 +32336,22 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -32365,53 +32366,49 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY276" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960371</t>
+          <t>https://artportalen.se/Sighting/128146053</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>128146053</v>
+        <v>128146050</v>
       </c>
       <c r="B277" t="n">
-        <v>93228</v>
+        <v>79350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>232140</v>
+        <v>260591</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -32421,10 +32418,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>691789</v>
+        <v>691554</v>
       </c>
       <c r="R277" t="n">
-        <v>7400698</v>
+        <v>7400883</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32456,7 +32453,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -32466,7 +32463,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -32492,51 +32489,54 @@
       <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146053</t>
+          <t>https://artportalen.se/Sighting/128146050</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128146050</v>
+        <v>128960420</v>
       </c>
       <c r="B278" t="n">
-        <v>79350</v>
+        <v>90601</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>260591</v>
+        <v>6331677</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spökfransskivling</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ripartites borealis</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>T.Ulvinen &amp; al.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>691554</v>
+        <v>691867</v>
       </c>
       <c r="R278" t="n">
-        <v>7400883</v>
+        <v>7400616</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32563,22 +32563,22 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -32587,33 +32587,38 @@
       <c r="AE278" t="b">
         <v>0</v>
       </c>
+      <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="b">
         <v>0</v>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY278" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146050</t>
+          <t>https://artportalen.se/Sighting/128960420</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128960420</v>
+        <v>128960584</v>
       </c>
       <c r="B279" t="n">
-        <v>90601</v>
+        <v>92183</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32621,37 +32626,34 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6331677</v>
+        <v>65</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Spökfransskivling</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Ripartites borealis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>T.Ulvinen &amp; al.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
           <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>691867</v>
+        <v>691877</v>
       </c>
       <c r="R279" t="n">
-        <v>7400616</v>
+        <v>7400599</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32683,7 +32685,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -32693,7 +32695,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -32702,7 +32704,6 @@
       <c r="AE279" t="b">
         <v>0</v>
       </c>
-      <c r="AF279" t="inlineStr"/>
       <c r="AG279" t="b">
         <v>0</v>
       </c>
@@ -32724,38 +32725,38 @@
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960420</t>
+          <t>https://artportalen.se/Sighting/128960584</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128960584</v>
+        <v>128960628</v>
       </c>
       <c r="B280" t="n">
-        <v>92183</v>
+        <v>93197</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -32765,10 +32766,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>691877</v>
+        <v>691884</v>
       </c>
       <c r="R280" t="n">
-        <v>7400599</v>
+        <v>7401043</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32800,7 +32801,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -32810,7 +32811,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -32839,122 +32840,6 @@
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/128960584</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>128960628</v>
-      </c>
-      <c r="B281" t="n">
-        <v>93197</v>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E281" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="P281" t="inlineStr">
-        <is>
-          <t>Gáddoajvve, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q281" t="n">
-        <v>691884</v>
-      </c>
-      <c r="R281" t="n">
-        <v>7401043</v>
-      </c>
-      <c r="S281" t="n">
-        <v>10</v>
-      </c>
-      <c r="T281" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U281" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V281" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y281" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AA281" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AD281" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE281" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG281" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT281" t="inlineStr"/>
-      <c r="AW281" t="inlineStr">
-        <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AX281" t="inlineStr">
-        <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY281" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
-      <c r="AZ281" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128960628</t>
         </is>
@@ -33241,7 +33126,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ280"/>
+  <dimension ref="A1:AZ281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16524,10 +16524,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128146055</v>
+        <v>130996947</v>
       </c>
       <c r="B139" t="n">
-        <v>93189</v>
+        <v>87347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16535,34 +16535,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4361</v>
+        <v>3746</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gulblå spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius transiens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Melot) Soop</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>690845</v>
+        <v>691080</v>
       </c>
       <c r="R139" t="n">
-        <v>7400680</v>
+        <v>7401099</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16589,22 +16592,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>DNA-sekvens av Petra Wikströms rapport https://www.artportalen.se/Sighting/128960678.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16613,30 +16611,35 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146055</t>
+          <t>https://artportalen.se/Sighting/130996947</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128146056</v>
+        <v>128146055</v>
       </c>
       <c r="B140" t="n">
         <v>93189</v>
@@ -16671,10 +16674,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>690781</v>
+        <v>690845</v>
       </c>
       <c r="R140" t="n">
-        <v>7400555</v>
+        <v>7400680</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16706,7 +16709,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16716,7 +16719,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16742,13 +16745,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146056</t>
+          <t>https://artportalen.se/Sighting/128146055</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128146057</v>
+        <v>128146056</v>
       </c>
       <c r="B141" t="n">
         <v>93189</v>
@@ -16783,10 +16786,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>690810</v>
+        <v>690781</v>
       </c>
       <c r="R141" t="n">
-        <v>7400772</v>
+        <v>7400555</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16818,7 +16821,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16828,7 +16831,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16854,16 +16857,16 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146057</t>
+          <t>https://artportalen.se/Sighting/128146056</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128146074</v>
+        <v>128146057</v>
       </c>
       <c r="B142" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16871,21 +16874,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16895,10 +16898,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>690796</v>
+        <v>690810</v>
       </c>
       <c r="R142" t="n">
-        <v>7400787</v>
+        <v>7400772</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16930,7 +16933,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16940,7 +16943,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16966,16 +16969,16 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146074</t>
+          <t>https://artportalen.se/Sighting/128146057</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128102520</v>
+        <v>128146074</v>
       </c>
       <c r="B143" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16983,34 +16986,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>690800</v>
+        <v>690796</v>
       </c>
       <c r="R143" t="n">
-        <v>7400819</v>
+        <v>7400787</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17040,9 +17043,19 @@
           <t>2025-08-31</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17068,13 +17081,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128102520</t>
+          <t>https://artportalen.se/Sighting/128146074</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128144837</v>
+        <v>128102520</v>
       </c>
       <c r="B144" t="n">
         <v>93197</v>
@@ -17105,14 +17118,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>691657</v>
+        <v>690800</v>
       </c>
       <c r="R144" t="n">
-        <v>7400758</v>
+        <v>7400819</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17142,19 +17155,9 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17180,13 +17183,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144837</t>
+          <t>https://artportalen.se/Sighting/128102520</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128146066</v>
+        <v>128144837</v>
       </c>
       <c r="B145" t="n">
         <v>93197</v>
@@ -17221,10 +17224,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>691535</v>
+        <v>691657</v>
       </c>
       <c r="R145" t="n">
-        <v>7400857</v>
+        <v>7400758</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17256,7 +17259,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17266,7 +17269,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17292,13 +17295,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146066</t>
+          <t>https://artportalen.se/Sighting/128144837</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128146067</v>
+        <v>128146066</v>
       </c>
       <c r="B146" t="n">
         <v>93197</v>
@@ -17333,10 +17336,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>691067</v>
+        <v>691535</v>
       </c>
       <c r="R146" t="n">
-        <v>7400865</v>
+        <v>7400857</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17368,7 +17371,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17378,7 +17381,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17404,13 +17407,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146067</t>
+          <t>https://artportalen.se/Sighting/128146066</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128146068</v>
+        <v>128146067</v>
       </c>
       <c r="B147" t="n">
         <v>93197</v>
@@ -17445,10 +17448,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>691003</v>
+        <v>691067</v>
       </c>
       <c r="R147" t="n">
-        <v>7400832</v>
+        <v>7400865</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17480,7 +17483,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17490,7 +17493,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17516,13 +17519,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146068</t>
+          <t>https://artportalen.se/Sighting/128146067</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128146069</v>
+        <v>128146068</v>
       </c>
       <c r="B148" t="n">
         <v>93197</v>
@@ -17560,7 +17563,7 @@
         <v>691003</v>
       </c>
       <c r="R148" t="n">
-        <v>7400833</v>
+        <v>7400832</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17628,13 +17631,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146069</t>
+          <t>https://artportalen.se/Sighting/128146068</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128146070</v>
+        <v>128146069</v>
       </c>
       <c r="B149" t="n">
         <v>93197</v>
@@ -17669,10 +17672,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>690846</v>
+        <v>691003</v>
       </c>
       <c r="R149" t="n">
-        <v>7400687</v>
+        <v>7400833</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17704,7 +17707,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17714,7 +17717,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17740,13 +17743,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146070</t>
+          <t>https://artportalen.se/Sighting/128146069</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128146071</v>
+        <v>128146070</v>
       </c>
       <c r="B150" t="n">
         <v>93197</v>
@@ -17781,10 +17784,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>690800</v>
+        <v>690846</v>
       </c>
       <c r="R150" t="n">
-        <v>7400737</v>
+        <v>7400687</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17816,7 +17819,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17826,7 +17829,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17852,13 +17855,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146071</t>
+          <t>https://artportalen.se/Sighting/128146070</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128960626</v>
+        <v>128146071</v>
       </c>
       <c r="B151" t="n">
         <v>93197</v>
@@ -17889,14 +17892,14 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>691772</v>
+        <v>690800</v>
       </c>
       <c r="R151" t="n">
-        <v>7400877</v>
+        <v>7400737</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17923,22 +17926,22 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17953,28 +17956,24 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960626</t>
+          <t>https://artportalen.se/Sighting/128146071</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128960629</v>
+        <v>128960626</v>
       </c>
       <c r="B152" t="n">
         <v>93197</v>
@@ -18009,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>691778</v>
+        <v>691772</v>
       </c>
       <c r="R152" t="n">
-        <v>7401031</v>
+        <v>7400877</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18044,7 +18043,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18054,7 +18053,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18084,13 +18083,13 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960629</t>
+          <t>https://artportalen.se/Sighting/128960626</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128960631</v>
+        <v>128960629</v>
       </c>
       <c r="B153" t="n">
         <v>93197</v>
@@ -18125,10 +18124,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>691572</v>
+        <v>691778</v>
       </c>
       <c r="R153" t="n">
-        <v>7401097</v>
+        <v>7401031</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18160,7 +18159,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18170,7 +18169,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18200,13 +18199,13 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960631</t>
+          <t>https://artportalen.se/Sighting/128960629</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128960633</v>
+        <v>128960631</v>
       </c>
       <c r="B154" t="n">
         <v>93197</v>
@@ -18241,10 +18240,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>691476</v>
+        <v>691572</v>
       </c>
       <c r="R154" t="n">
-        <v>7400909</v>
+        <v>7401097</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18276,7 +18275,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18286,7 +18285,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18316,13 +18315,13 @@
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960633</t>
+          <t>https://artportalen.se/Sighting/128960631</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128960634</v>
+        <v>128960633</v>
       </c>
       <c r="B155" t="n">
         <v>93197</v>
@@ -18357,10 +18356,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>691432</v>
+        <v>691476</v>
       </c>
       <c r="R155" t="n">
-        <v>7400884</v>
+        <v>7400909</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18392,7 +18391,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18402,7 +18401,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18432,13 +18431,13 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960634</t>
+          <t>https://artportalen.se/Sighting/128960633</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128960636</v>
+        <v>128960634</v>
       </c>
       <c r="B156" t="n">
         <v>93197</v>
@@ -18473,10 +18472,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>691313</v>
+        <v>691432</v>
       </c>
       <c r="R156" t="n">
-        <v>7400890</v>
+        <v>7400884</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18508,7 +18507,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18518,7 +18517,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18548,13 +18547,13 @@
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960636</t>
+          <t>https://artportalen.se/Sighting/128960634</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128960637</v>
+        <v>128960636</v>
       </c>
       <c r="B157" t="n">
         <v>93197</v>
@@ -18589,10 +18588,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>691085</v>
+        <v>691313</v>
       </c>
       <c r="R157" t="n">
-        <v>7400630</v>
+        <v>7400890</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18624,7 +18623,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18634,7 +18633,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18664,13 +18663,13 @@
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960637</t>
+          <t>https://artportalen.se/Sighting/128960636</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128960639</v>
+        <v>128960637</v>
       </c>
       <c r="B158" t="n">
         <v>93197</v>
@@ -18705,10 +18704,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>691173</v>
+        <v>691085</v>
       </c>
       <c r="R158" t="n">
-        <v>7400751</v>
+        <v>7400630</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18740,7 +18739,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18750,7 +18749,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18780,13 +18779,13 @@
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960639</t>
+          <t>https://artportalen.se/Sighting/128960637</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128960641</v>
+        <v>128960639</v>
       </c>
       <c r="B159" t="n">
         <v>93197</v>
@@ -18821,10 +18820,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>691271</v>
+        <v>691173</v>
       </c>
       <c r="R159" t="n">
-        <v>7400775</v>
+        <v>7400751</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18856,7 +18855,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18866,7 +18865,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18896,13 +18895,13 @@
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960641</t>
+          <t>https://artportalen.se/Sighting/128960639</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128960642</v>
+        <v>128960641</v>
       </c>
       <c r="B160" t="n">
         <v>93197</v>
@@ -18937,10 +18936,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>691479</v>
+        <v>691271</v>
       </c>
       <c r="R160" t="n">
-        <v>7400776</v>
+        <v>7400775</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18972,7 +18971,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18982,7 +18981,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19012,13 +19011,13 @@
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960642</t>
+          <t>https://artportalen.se/Sighting/128960641</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128960644</v>
+        <v>128960642</v>
       </c>
       <c r="B161" t="n">
         <v>93197</v>
@@ -19053,10 +19052,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>691471</v>
+        <v>691479</v>
       </c>
       <c r="R161" t="n">
-        <v>7400823</v>
+        <v>7400776</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19088,7 +19087,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19098,7 +19097,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19128,13 +19127,13 @@
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960644</t>
+          <t>https://artportalen.se/Sighting/128960642</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128960646</v>
+        <v>128960644</v>
       </c>
       <c r="B162" t="n">
         <v>93197</v>
@@ -19169,10 +19168,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>691445</v>
+        <v>691471</v>
       </c>
       <c r="R162" t="n">
-        <v>7400907</v>
+        <v>7400823</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19204,7 +19203,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19214,7 +19213,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19244,13 +19243,13 @@
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960646</t>
+          <t>https://artportalen.se/Sighting/128960644</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128960650</v>
+        <v>128960646</v>
       </c>
       <c r="B163" t="n">
         <v>93197</v>
@@ -19285,10 +19284,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>690728</v>
+        <v>691445</v>
       </c>
       <c r="R163" t="n">
-        <v>7400633</v>
+        <v>7400907</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19315,22 +19314,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19360,13 +19359,13 @@
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960650</t>
+          <t>https://artportalen.se/Sighting/128960646</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128960653</v>
+        <v>128960650</v>
       </c>
       <c r="B164" t="n">
         <v>93197</v>
@@ -19401,10 +19400,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>690703</v>
+        <v>690728</v>
       </c>
       <c r="R164" t="n">
-        <v>7400802</v>
+        <v>7400633</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19436,7 +19435,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19446,7 +19445,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19476,13 +19475,13 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960653</t>
+          <t>https://artportalen.se/Sighting/128960650</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128960655</v>
+        <v>128960653</v>
       </c>
       <c r="B165" t="n">
         <v>93197</v>
@@ -19517,10 +19516,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>690734</v>
+        <v>690703</v>
       </c>
       <c r="R165" t="n">
-        <v>7400797</v>
+        <v>7400802</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19552,7 +19551,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19562,7 +19561,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19592,13 +19591,13 @@
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960655</t>
+          <t>https://artportalen.se/Sighting/128960653</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128960658</v>
+        <v>128960655</v>
       </c>
       <c r="B166" t="n">
         <v>93197</v>
@@ -19633,10 +19632,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>690788</v>
+        <v>690734</v>
       </c>
       <c r="R166" t="n">
-        <v>7400864</v>
+        <v>7400797</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19668,7 +19667,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19678,7 +19677,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19708,13 +19707,13 @@
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960658</t>
+          <t>https://artportalen.se/Sighting/128960655</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128960661</v>
+        <v>128960658</v>
       </c>
       <c r="B167" t="n">
         <v>93197</v>
@@ -19749,10 +19748,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>691007</v>
+        <v>690788</v>
       </c>
       <c r="R167" t="n">
-        <v>7401047</v>
+        <v>7400864</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19784,7 +19783,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19794,7 +19793,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19824,16 +19823,16 @@
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960661</t>
+          <t>https://artportalen.se/Sighting/128960658</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128960416</v>
+        <v>128960661</v>
       </c>
       <c r="B168" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19841,21 +19840,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19865,10 +19864,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>690733</v>
+        <v>691007</v>
       </c>
       <c r="R168" t="n">
-        <v>7400794</v>
+        <v>7401047</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19900,7 +19899,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19910,7 +19909,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19940,38 +19939,38 @@
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960416</t>
+          <t>https://artportalen.se/Sighting/128960661</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128960677</v>
+        <v>128960416</v>
       </c>
       <c r="B169" t="n">
-        <v>89143</v>
+        <v>93209</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4405</v>
+        <v>4366</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19981,10 +19980,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>691492</v>
+        <v>690733</v>
       </c>
       <c r="R169" t="n">
-        <v>7400692</v>
+        <v>7400794</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20011,22 +20010,22 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20056,51 +20055,51 @@
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960677</t>
+          <t>https://artportalen.se/Sighting/128960416</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128146051</v>
+        <v>128960677</v>
       </c>
       <c r="B170" t="n">
-        <v>92841</v>
+        <v>89143</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4745</v>
+        <v>4405</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>691386</v>
+        <v>691492</v>
       </c>
       <c r="R170" t="n">
-        <v>7400998</v>
+        <v>7400692</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20127,22 +20126,22 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20157,24 +20156,28 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146051</t>
+          <t>https://artportalen.se/Sighting/128960677</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128960394</v>
+        <v>128146051</v>
       </c>
       <c r="B171" t="n">
         <v>92841</v>
@@ -20205,14 +20208,14 @@
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>691657</v>
+        <v>691386</v>
       </c>
       <c r="R171" t="n">
-        <v>7400847</v>
+        <v>7400998</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20239,22 +20242,22 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20269,28 +20272,24 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY171" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960394</t>
+          <t>https://artportalen.se/Sighting/128146051</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128960396</v>
+        <v>128960394</v>
       </c>
       <c r="B172" t="n">
         <v>92841</v>
@@ -20325,10 +20324,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>691486</v>
+        <v>691657</v>
       </c>
       <c r="R172" t="n">
-        <v>7400758</v>
+        <v>7400847</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20360,7 +20359,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -20370,7 +20369,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20400,13 +20399,13 @@
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960396</t>
+          <t>https://artportalen.se/Sighting/128960394</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128960397</v>
+        <v>128960396</v>
       </c>
       <c r="B173" t="n">
         <v>92841</v>
@@ -20441,10 +20440,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>690679</v>
+        <v>691486</v>
       </c>
       <c r="R173" t="n">
-        <v>7400680</v>
+        <v>7400758</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20471,22 +20470,22 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20516,13 +20515,13 @@
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960397</t>
+          <t>https://artportalen.se/Sighting/128960396</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128960398</v>
+        <v>128960397</v>
       </c>
       <c r="B174" t="n">
         <v>92841</v>
@@ -20557,10 +20556,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>690713</v>
+        <v>690679</v>
       </c>
       <c r="R174" t="n">
-        <v>7400706</v>
+        <v>7400680</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20592,7 +20591,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -20602,7 +20601,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20632,13 +20631,13 @@
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960398</t>
+          <t>https://artportalen.se/Sighting/128960397</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128960399</v>
+        <v>128960398</v>
       </c>
       <c r="B175" t="n">
         <v>92841</v>
@@ -20673,10 +20672,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>690819</v>
+        <v>690713</v>
       </c>
       <c r="R175" t="n">
-        <v>7400882</v>
+        <v>7400706</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20708,7 +20707,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -20718,7 +20717,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20748,16 +20747,16 @@
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960399</t>
+          <t>https://artportalen.se/Sighting/128960398</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128960436</v>
+        <v>128960399</v>
       </c>
       <c r="B176" t="n">
-        <v>90522</v>
+        <v>92841</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20765,21 +20764,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4962</v>
+        <v>4745</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -20789,10 +20788,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>691019</v>
+        <v>690819</v>
       </c>
       <c r="R176" t="n">
-        <v>7400845</v>
+        <v>7400882</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20819,22 +20818,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20864,13 +20863,13 @@
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960436</t>
+          <t>https://artportalen.se/Sighting/128960399</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128960437</v>
+        <v>128960436</v>
       </c>
       <c r="B177" t="n">
         <v>90522</v>
@@ -20905,10 +20904,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>691225</v>
+        <v>691019</v>
       </c>
       <c r="R177" t="n">
-        <v>7400593</v>
+        <v>7400845</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20940,7 +20939,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20950,7 +20949,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20980,13 +20979,13 @@
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960437</t>
+          <t>https://artportalen.se/Sighting/128960436</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128960439</v>
+        <v>128960437</v>
       </c>
       <c r="B178" t="n">
         <v>90522</v>
@@ -21021,10 +21020,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>690708</v>
+        <v>691225</v>
       </c>
       <c r="R178" t="n">
-        <v>7400815</v>
+        <v>7400593</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21051,22 +21050,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21096,38 +21095,38 @@
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960439</t>
+          <t>https://artportalen.se/Sighting/128960437</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128960356</v>
+        <v>128960439</v>
       </c>
       <c r="B179" t="n">
-        <v>91872</v>
+        <v>90522</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5447</v>
+        <v>4962</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21137,10 +21136,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>691028</v>
+        <v>690708</v>
       </c>
       <c r="R179" t="n">
-        <v>7400838</v>
+        <v>7400815</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21167,22 +21166,22 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21212,38 +21211,38 @@
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960356</t>
+          <t>https://artportalen.se/Sighting/128960439</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128960402</v>
+        <v>128960356</v>
       </c>
       <c r="B180" t="n">
-        <v>93223</v>
+        <v>91872</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -21253,10 +21252,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>690717</v>
+        <v>691028</v>
       </c>
       <c r="R180" t="n">
-        <v>7400812</v>
+        <v>7400838</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -21283,22 +21282,22 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21328,16 +21327,16 @@
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960402</t>
+          <t>https://artportalen.se/Sighting/128960356</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128960550</v>
+        <v>128960402</v>
       </c>
       <c r="B181" t="n">
-        <v>92556</v>
+        <v>93223</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21345,21 +21344,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5454</v>
+        <v>5448</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -21369,10 +21368,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>691708</v>
+        <v>690717</v>
       </c>
       <c r="R181" t="n">
-        <v>7401045</v>
+        <v>7400812</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21399,22 +21398,22 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21444,16 +21443,16 @@
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960550</t>
+          <t>https://artportalen.se/Sighting/128960402</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128144838</v>
+        <v>128960550</v>
       </c>
       <c r="B182" t="n">
-        <v>78730</v>
+        <v>92556</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21461,34 +21460,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6437</v>
+        <v>5454</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>691841</v>
+        <v>691708</v>
       </c>
       <c r="R182" t="n">
-        <v>7400785</v>
+        <v>7401045</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21515,22 +21514,22 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21545,24 +21544,28 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY182" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144838</t>
+          <t>https://artportalen.se/Sighting/128960550</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128144839</v>
+        <v>128144838</v>
       </c>
       <c r="B183" t="n">
         <v>78730</v>
@@ -21597,10 +21600,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>691806</v>
+        <v>691841</v>
       </c>
       <c r="R183" t="n">
-        <v>7400707</v>
+        <v>7400785</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21632,7 +21635,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -21642,7 +21645,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21668,13 +21671,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144839</t>
+          <t>https://artportalen.se/Sighting/128144838</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128144840</v>
+        <v>128144839</v>
       </c>
       <c r="B184" t="n">
         <v>78730</v>
@@ -21709,10 +21712,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>691520</v>
+        <v>691806</v>
       </c>
       <c r="R184" t="n">
-        <v>7400858</v>
+        <v>7400707</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21744,7 +21747,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -21754,7 +21757,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21780,13 +21783,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144840</t>
+          <t>https://artportalen.se/Sighting/128144839</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128146075</v>
+        <v>128144840</v>
       </c>
       <c r="B185" t="n">
         <v>78730</v>
@@ -21821,10 +21824,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>691077</v>
+        <v>691520</v>
       </c>
       <c r="R185" t="n">
-        <v>7400880</v>
+        <v>7400858</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21856,7 +21859,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21866,7 +21869,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21892,13 +21895,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146075</t>
+          <t>https://artportalen.se/Sighting/128144840</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128960690</v>
+        <v>128146075</v>
       </c>
       <c r="B186" t="n">
         <v>78730</v>
@@ -21929,14 +21932,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>690817</v>
+        <v>691077</v>
       </c>
       <c r="R186" t="n">
-        <v>7400668</v>
+        <v>7400880</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21963,22 +21966,22 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21993,28 +21996,24 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY186" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960690</t>
+          <t>https://artportalen.se/Sighting/128146075</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128960693</v>
+        <v>128960690</v>
       </c>
       <c r="B187" t="n">
         <v>78730</v>
@@ -22049,10 +22048,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>691595</v>
+        <v>690817</v>
       </c>
       <c r="R187" t="n">
-        <v>7401115</v>
+        <v>7400668</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -22079,22 +22078,22 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -22124,16 +22123,16 @@
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960693</t>
+          <t>https://artportalen.se/Sighting/128960690</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128144829</v>
+        <v>128960693</v>
       </c>
       <c r="B188" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22141,34 +22140,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>691811</v>
+        <v>691595</v>
       </c>
       <c r="R188" t="n">
-        <v>7400740</v>
+        <v>7401115</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -22195,22 +22194,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -22225,27 +22224,31 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY188" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144829</t>
+          <t>https://artportalen.se/Sighting/128960693</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128144819</v>
+        <v>128144829</v>
       </c>
       <c r="B189" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22253,21 +22256,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -22277,10 +22280,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>691675</v>
+        <v>691811</v>
       </c>
       <c r="R189" t="n">
-        <v>7401012</v>
+        <v>7400740</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22312,7 +22315,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -22322,7 +22325,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -22348,13 +22351,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144819</t>
+          <t>https://artportalen.se/Sighting/128144829</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128144820</v>
+        <v>128144819</v>
       </c>
       <c r="B190" t="n">
         <v>79946</v>
@@ -22389,10 +22392,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>691749</v>
+        <v>691675</v>
       </c>
       <c r="R190" t="n">
-        <v>7400999</v>
+        <v>7401012</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -22424,7 +22427,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -22434,7 +22437,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22460,13 +22463,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144820</t>
+          <t>https://artportalen.se/Sighting/128144819</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128144822</v>
+        <v>128144820</v>
       </c>
       <c r="B191" t="n">
         <v>79946</v>
@@ -22501,10 +22504,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>691662</v>
+        <v>691749</v>
       </c>
       <c r="R191" t="n">
-        <v>7400760</v>
+        <v>7400999</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22536,7 +22539,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -22546,7 +22549,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22572,13 +22575,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144822</t>
+          <t>https://artportalen.se/Sighting/128144820</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128144823</v>
+        <v>128144822</v>
       </c>
       <c r="B192" t="n">
         <v>79946</v>
@@ -22613,10 +22616,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>691519</v>
+        <v>691662</v>
       </c>
       <c r="R192" t="n">
-        <v>7400859</v>
+        <v>7400760</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22648,7 +22651,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -22658,7 +22661,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22684,13 +22687,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144823</t>
+          <t>https://artportalen.se/Sighting/128144822</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128146042</v>
+        <v>128144823</v>
       </c>
       <c r="B193" t="n">
         <v>79946</v>
@@ -22725,10 +22728,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>691337</v>
+        <v>691519</v>
       </c>
       <c r="R193" t="n">
-        <v>7400753</v>
+        <v>7400859</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22760,7 +22763,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -22770,7 +22773,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22796,13 +22799,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146042</t>
+          <t>https://artportalen.se/Sighting/128144823</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128960357</v>
+        <v>128146042</v>
       </c>
       <c r="B194" t="n">
         <v>79946</v>
@@ -22833,14 +22836,14 @@
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>691748</v>
+        <v>691337</v>
       </c>
       <c r="R194" t="n">
-        <v>7400820</v>
+        <v>7400753</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22867,22 +22870,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22897,28 +22900,24 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY194" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960357</t>
+          <t>https://artportalen.se/Sighting/128146042</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128960358</v>
+        <v>128960357</v>
       </c>
       <c r="B195" t="n">
         <v>79946</v>
@@ -22953,10 +22952,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>691772</v>
+        <v>691748</v>
       </c>
       <c r="R195" t="n">
-        <v>7400877</v>
+        <v>7400820</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22988,7 +22987,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -22998,7 +22997,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -23028,13 +23027,13 @@
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960358</t>
+          <t>https://artportalen.se/Sighting/128960357</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128960359</v>
+        <v>128960358</v>
       </c>
       <c r="B196" t="n">
         <v>79946</v>
@@ -23069,10 +23068,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>691774</v>
+        <v>691772</v>
       </c>
       <c r="R196" t="n">
-        <v>7401018</v>
+        <v>7400877</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -23104,7 +23103,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -23114,7 +23113,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -23144,51 +23143,51 @@
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960359</t>
+          <t>https://artportalen.se/Sighting/128960358</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128144824</v>
+        <v>128960359</v>
       </c>
       <c r="B197" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>691607</v>
+        <v>691774</v>
       </c>
       <c r="R197" t="n">
-        <v>7400989</v>
+        <v>7401018</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23215,22 +23214,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -23245,24 +23244,28 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY197" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144824</t>
+          <t>https://artportalen.se/Sighting/128960359</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128144825</v>
+        <v>128144824</v>
       </c>
       <c r="B198" t="n">
         <v>80336</v>
@@ -23297,10 +23300,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>691427</v>
+        <v>691607</v>
       </c>
       <c r="R198" t="n">
-        <v>7401053</v>
+        <v>7400989</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23332,7 +23335,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -23342,7 +23345,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23368,38 +23371,38 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144825</t>
+          <t>https://artportalen.se/Sighting/128144824</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128146058</v>
+        <v>128144825</v>
       </c>
       <c r="B199" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -23409,10 +23412,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>691437</v>
+        <v>691427</v>
       </c>
       <c r="R199" t="n">
-        <v>7401034</v>
+        <v>7401053</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -23444,7 +23447,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -23454,7 +23457,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -23480,51 +23483,51 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146058</t>
+          <t>https://artportalen.se/Sighting/128144825</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128960405</v>
+        <v>128146058</v>
       </c>
       <c r="B200" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>690835</v>
+        <v>691437</v>
       </c>
       <c r="R200" t="n">
-        <v>7400894</v>
+        <v>7401034</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -23551,22 +23554,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23581,28 +23584,24 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY200" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960405</t>
+          <t>https://artportalen.se/Sighting/128146058</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128960406</v>
+        <v>128960405</v>
       </c>
       <c r="B201" t="n">
         <v>80461</v>
@@ -23637,10 +23636,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>691215</v>
+        <v>690835</v>
       </c>
       <c r="R201" t="n">
-        <v>7400790</v>
+        <v>7400894</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23667,22 +23666,22 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23712,13 +23711,13 @@
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960406</t>
+          <t>https://artportalen.se/Sighting/128960405</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128960407</v>
+        <v>128960406</v>
       </c>
       <c r="B202" t="n">
         <v>80461</v>
@@ -23753,10 +23752,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>691472</v>
+        <v>691215</v>
       </c>
       <c r="R202" t="n">
-        <v>7401056</v>
+        <v>7400790</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23788,7 +23787,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -23798,7 +23797,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23828,16 +23827,16 @@
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960407</t>
+          <t>https://artportalen.se/Sighting/128960406</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128960683</v>
+        <v>128960407</v>
       </c>
       <c r="B203" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23845,21 +23844,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23869,10 +23868,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>690835</v>
+        <v>691472</v>
       </c>
       <c r="R203" t="n">
-        <v>7400892</v>
+        <v>7401056</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23899,22 +23898,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23944,51 +23943,51 @@
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960683</t>
+          <t>https://artportalen.se/Sighting/128960407</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128146073</v>
+        <v>128960683</v>
       </c>
       <c r="B204" t="n">
-        <v>78334</v>
+        <v>80467</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6487</v>
+        <v>6463</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>691079</v>
+        <v>690835</v>
       </c>
       <c r="R204" t="n">
-        <v>7400877</v>
+        <v>7400892</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -24015,22 +24014,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -24045,24 +24044,28 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY204" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146073</t>
+          <t>https://artportalen.se/Sighting/128960683</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128960684</v>
+        <v>128146073</v>
       </c>
       <c r="B205" t="n">
         <v>78334</v>
@@ -24093,14 +24096,14 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>691442</v>
+        <v>691079</v>
       </c>
       <c r="R205" t="n">
-        <v>7400932</v>
+        <v>7400877</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -24127,22 +24130,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24157,28 +24160,24 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY205" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960684</t>
+          <t>https://artportalen.se/Sighting/128146073</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128960685</v>
+        <v>128960684</v>
       </c>
       <c r="B206" t="n">
         <v>78334</v>
@@ -24213,10 +24212,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>690998</v>
+        <v>691442</v>
       </c>
       <c r="R206" t="n">
-        <v>7401040</v>
+        <v>7400932</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24243,22 +24242,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24288,13 +24287,13 @@
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960685</t>
+          <t>https://artportalen.se/Sighting/128960684</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128960687</v>
+        <v>128960685</v>
       </c>
       <c r="B207" t="n">
         <v>78334</v>
@@ -24329,10 +24328,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>691772</v>
+        <v>690998</v>
       </c>
       <c r="R207" t="n">
-        <v>7401045</v>
+        <v>7401040</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24359,22 +24358,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24404,16 +24403,16 @@
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960687</t>
+          <t>https://artportalen.se/Sighting/128960685</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128144826</v>
+        <v>128960687</v>
       </c>
       <c r="B208" t="n">
-        <v>5495</v>
+        <v>78334</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24421,34 +24420,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>101410</v>
+        <v>6487</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>691845</v>
+        <v>691772</v>
       </c>
       <c r="R208" t="n">
-        <v>7400932</v>
+        <v>7401045</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24475,22 +24474,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24505,49 +24504,53 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY208" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144826</t>
+          <t>https://artportalen.se/Sighting/128960687</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128144830</v>
+        <v>128144826</v>
       </c>
       <c r="B209" t="n">
-        <v>99118</v>
+        <v>5495</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -24557,10 +24560,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>691395</v>
+        <v>691845</v>
       </c>
       <c r="R209" t="n">
-        <v>7401068</v>
+        <v>7400932</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -24592,7 +24595,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -24602,12 +24605,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24633,13 +24631,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144830</t>
+          <t>https://artportalen.se/Sighting/128144826</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128144833</v>
+        <v>128144830</v>
       </c>
       <c r="B210" t="n">
         <v>99118</v>
@@ -24674,10 +24672,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>691471</v>
+        <v>691395</v>
       </c>
       <c r="R210" t="n">
-        <v>7401138</v>
+        <v>7401068</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -24709,7 +24707,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -24719,7 +24717,12 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24745,13 +24748,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144833</t>
+          <t>https://artportalen.se/Sighting/128144830</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128146060</v>
+        <v>128144833</v>
       </c>
       <c r="B211" t="n">
         <v>99118</v>
@@ -24786,10 +24789,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>691443</v>
+        <v>691471</v>
       </c>
       <c r="R211" t="n">
-        <v>7401033</v>
+        <v>7401138</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -24821,7 +24824,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -24831,7 +24834,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24857,13 +24860,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146060</t>
+          <t>https://artportalen.se/Sighting/128144833</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128960451</v>
+        <v>128146060</v>
       </c>
       <c r="B212" t="n">
         <v>99118</v>
@@ -24894,14 +24897,14 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>691520</v>
+        <v>691443</v>
       </c>
       <c r="R212" t="n">
-        <v>7401010</v>
+        <v>7401033</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24928,22 +24931,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24958,28 +24961,24 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY212" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960451</t>
+          <t>https://artportalen.se/Sighting/128146060</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128960455</v>
+        <v>128960451</v>
       </c>
       <c r="B213" t="n">
         <v>99118</v>
@@ -25014,10 +25013,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>691615</v>
+        <v>691520</v>
       </c>
       <c r="R213" t="n">
-        <v>7400959</v>
+        <v>7401010</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -25049,7 +25048,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -25059,7 +25058,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -25089,13 +25088,13 @@
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960455</t>
+          <t>https://artportalen.se/Sighting/128960451</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128960456</v>
+        <v>128960455</v>
       </c>
       <c r="B214" t="n">
         <v>99118</v>
@@ -25130,10 +25129,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>691641</v>
+        <v>691615</v>
       </c>
       <c r="R214" t="n">
-        <v>7400939</v>
+        <v>7400959</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25165,7 +25164,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -25175,7 +25174,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -25205,13 +25204,13 @@
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960456</t>
+          <t>https://artportalen.se/Sighting/128960455</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128960459</v>
+        <v>128960456</v>
       </c>
       <c r="B215" t="n">
         <v>99118</v>
@@ -25246,10 +25245,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>691498</v>
+        <v>691641</v>
       </c>
       <c r="R215" t="n">
-        <v>7401073</v>
+        <v>7400939</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25281,7 +25280,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -25291,7 +25290,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -25321,13 +25320,13 @@
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960459</t>
+          <t>https://artportalen.se/Sighting/128960456</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128960460</v>
+        <v>128960459</v>
       </c>
       <c r="B216" t="n">
         <v>99118</v>
@@ -25362,10 +25361,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>691513</v>
+        <v>691498</v>
       </c>
       <c r="R216" t="n">
-        <v>7401038</v>
+        <v>7401073</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25397,7 +25396,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -25407,7 +25406,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -25437,13 +25436,13 @@
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960460</t>
+          <t>https://artportalen.se/Sighting/128960459</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128960461</v>
+        <v>128960460</v>
       </c>
       <c r="B217" t="n">
         <v>99118</v>
@@ -25478,10 +25477,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>691285</v>
+        <v>691513</v>
       </c>
       <c r="R217" t="n">
-        <v>7400841</v>
+        <v>7401038</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25513,7 +25512,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -25523,7 +25522,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25553,13 +25552,13 @@
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960461</t>
+          <t>https://artportalen.se/Sighting/128960460</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128960463</v>
+        <v>128960461</v>
       </c>
       <c r="B218" t="n">
         <v>99118</v>
@@ -25594,10 +25593,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>691259</v>
+        <v>691285</v>
       </c>
       <c r="R218" t="n">
-        <v>7400802</v>
+        <v>7400841</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -25629,7 +25628,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -25639,7 +25638,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25669,13 +25668,13 @@
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960463</t>
+          <t>https://artportalen.se/Sighting/128960461</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128960464</v>
+        <v>128960463</v>
       </c>
       <c r="B219" t="n">
         <v>99118</v>
@@ -25710,10 +25709,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>691251</v>
+        <v>691259</v>
       </c>
       <c r="R219" t="n">
-        <v>7400808</v>
+        <v>7400802</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25745,7 +25744,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -25755,7 +25754,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -25785,13 +25784,13 @@
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960464</t>
+          <t>https://artportalen.se/Sighting/128960463</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128960465</v>
+        <v>128960464</v>
       </c>
       <c r="B220" t="n">
         <v>99118</v>
@@ -25826,10 +25825,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>691184</v>
+        <v>691251</v>
       </c>
       <c r="R220" t="n">
-        <v>7400869</v>
+        <v>7400808</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25861,7 +25860,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -25871,7 +25870,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -25901,13 +25900,13 @@
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960465</t>
+          <t>https://artportalen.se/Sighting/128960464</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128960467</v>
+        <v>128960465</v>
       </c>
       <c r="B221" t="n">
         <v>99118</v>
@@ -25942,10 +25941,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>691182</v>
+        <v>691184</v>
       </c>
       <c r="R221" t="n">
-        <v>7400878</v>
+        <v>7400869</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -26017,13 +26016,13 @@
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960467</t>
+          <t>https://artportalen.se/Sighting/128960465</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128960468</v>
+        <v>128960467</v>
       </c>
       <c r="B222" t="n">
         <v>99118</v>
@@ -26058,10 +26057,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>691175</v>
+        <v>691182</v>
       </c>
       <c r="R222" t="n">
-        <v>7400884</v>
+        <v>7400878</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26093,7 +26092,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -26103,7 +26102,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -26133,13 +26132,13 @@
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960468</t>
+          <t>https://artportalen.se/Sighting/128960467</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128960469</v>
+        <v>128960468</v>
       </c>
       <c r="B223" t="n">
         <v>99118</v>
@@ -26174,10 +26173,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>691149</v>
+        <v>691175</v>
       </c>
       <c r="R223" t="n">
-        <v>7400912</v>
+        <v>7400884</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26209,7 +26208,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -26219,7 +26218,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -26249,13 +26248,13 @@
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960469</t>
+          <t>https://artportalen.se/Sighting/128960468</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128960470</v>
+        <v>128960469</v>
       </c>
       <c r="B224" t="n">
         <v>99118</v>
@@ -26290,10 +26289,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>691148</v>
+        <v>691149</v>
       </c>
       <c r="R224" t="n">
-        <v>7400926</v>
+        <v>7400912</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26325,7 +26324,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -26335,7 +26334,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26365,13 +26364,13 @@
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960470</t>
+          <t>https://artportalen.se/Sighting/128960469</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128960471</v>
+        <v>128960470</v>
       </c>
       <c r="B225" t="n">
         <v>99118</v>
@@ -26406,10 +26405,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>691137</v>
+        <v>691148</v>
       </c>
       <c r="R225" t="n">
-        <v>7400938</v>
+        <v>7400926</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -26481,13 +26480,13 @@
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960471</t>
+          <t>https://artportalen.se/Sighting/128960470</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128960472</v>
+        <v>128960471</v>
       </c>
       <c r="B226" t="n">
         <v>99118</v>
@@ -26522,10 +26521,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>690998</v>
+        <v>691137</v>
       </c>
       <c r="R226" t="n">
-        <v>7400789</v>
+        <v>7400938</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -26557,7 +26556,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -26567,7 +26566,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -26597,13 +26596,13 @@
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960472</t>
+          <t>https://artportalen.se/Sighting/128960471</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128960473</v>
+        <v>128960472</v>
       </c>
       <c r="B227" t="n">
         <v>99118</v>
@@ -26641,7 +26640,7 @@
         <v>690998</v>
       </c>
       <c r="R227" t="n">
-        <v>7400742</v>
+        <v>7400789</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26673,7 +26672,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -26683,7 +26682,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -26713,13 +26712,13 @@
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960473</t>
+          <t>https://artportalen.se/Sighting/128960472</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128960474</v>
+        <v>128960473</v>
       </c>
       <c r="B228" t="n">
         <v>99118</v>
@@ -26754,10 +26753,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>691032</v>
+        <v>690998</v>
       </c>
       <c r="R228" t="n">
-        <v>7400748</v>
+        <v>7400742</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26789,7 +26788,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -26799,7 +26798,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26829,13 +26828,13 @@
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960474</t>
+          <t>https://artportalen.se/Sighting/128960473</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128960475</v>
+        <v>128960474</v>
       </c>
       <c r="B229" t="n">
         <v>99118</v>
@@ -26870,10 +26869,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>691050</v>
+        <v>691032</v>
       </c>
       <c r="R229" t="n">
-        <v>7400705</v>
+        <v>7400748</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26905,7 +26904,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -26915,7 +26914,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26945,13 +26944,13 @@
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960475</t>
+          <t>https://artportalen.se/Sighting/128960474</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128960476</v>
+        <v>128960475</v>
       </c>
       <c r="B230" t="n">
         <v>99118</v>
@@ -26986,10 +26985,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>691094</v>
+        <v>691050</v>
       </c>
       <c r="R230" t="n">
-        <v>7400693</v>
+        <v>7400705</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -27021,7 +27020,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -27031,7 +27030,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -27061,13 +27060,13 @@
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960476</t>
+          <t>https://artportalen.se/Sighting/128960475</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128960477</v>
+        <v>128960476</v>
       </c>
       <c r="B231" t="n">
         <v>99118</v>
@@ -27102,10 +27101,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>691104</v>
+        <v>691094</v>
       </c>
       <c r="R231" t="n">
-        <v>7400683</v>
+        <v>7400693</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -27137,7 +27136,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -27147,7 +27146,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -27177,13 +27176,13 @@
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960477</t>
+          <t>https://artportalen.se/Sighting/128960476</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128960478</v>
+        <v>128960477</v>
       </c>
       <c r="B232" t="n">
         <v>99118</v>
@@ -27218,10 +27217,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>691303</v>
+        <v>691104</v>
       </c>
       <c r="R232" t="n">
-        <v>7400537</v>
+        <v>7400683</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -27253,7 +27252,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -27263,7 +27262,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -27293,13 +27292,13 @@
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960478</t>
+          <t>https://artportalen.se/Sighting/128960477</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128960479</v>
+        <v>128960478</v>
       </c>
       <c r="B233" t="n">
         <v>99118</v>
@@ -27334,10 +27333,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>691286</v>
+        <v>691303</v>
       </c>
       <c r="R233" t="n">
-        <v>7400554</v>
+        <v>7400537</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -27369,7 +27368,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -27379,7 +27378,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27409,13 +27408,13 @@
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960479</t>
+          <t>https://artportalen.se/Sighting/128960478</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128960480</v>
+        <v>128960479</v>
       </c>
       <c r="B234" t="n">
         <v>99118</v>
@@ -27450,10 +27449,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>691030</v>
+        <v>691286</v>
       </c>
       <c r="R234" t="n">
-        <v>7400688</v>
+        <v>7400554</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -27485,7 +27484,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -27495,7 +27494,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -27525,13 +27524,13 @@
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960480</t>
+          <t>https://artportalen.se/Sighting/128960479</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128960481</v>
+        <v>128960480</v>
       </c>
       <c r="B235" t="n">
         <v>99118</v>
@@ -27566,10 +27565,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>691054</v>
+        <v>691030</v>
       </c>
       <c r="R235" t="n">
-        <v>7400678</v>
+        <v>7400688</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -27641,13 +27640,13 @@
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960481</t>
+          <t>https://artportalen.se/Sighting/128960480</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128960483</v>
+        <v>128960481</v>
       </c>
       <c r="B236" t="n">
         <v>99118</v>
@@ -27682,10 +27681,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>691042</v>
+        <v>691054</v>
       </c>
       <c r="R236" t="n">
-        <v>7400691</v>
+        <v>7400678</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27717,7 +27716,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -27727,7 +27726,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -27757,13 +27756,13 @@
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960483</t>
+          <t>https://artportalen.se/Sighting/128960481</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128960484</v>
+        <v>128960483</v>
       </c>
       <c r="B237" t="n">
         <v>99118</v>
@@ -27798,10 +27797,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>691205</v>
+        <v>691042</v>
       </c>
       <c r="R237" t="n">
-        <v>7400756</v>
+        <v>7400691</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27833,7 +27832,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27843,7 +27842,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27873,13 +27872,13 @@
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960484</t>
+          <t>https://artportalen.se/Sighting/128960483</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128960485</v>
+        <v>128960484</v>
       </c>
       <c r="B238" t="n">
         <v>99118</v>
@@ -27914,10 +27913,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>691491</v>
+        <v>691205</v>
       </c>
       <c r="R238" t="n">
-        <v>7400689</v>
+        <v>7400756</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27949,7 +27948,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27959,7 +27958,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27989,13 +27988,13 @@
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960485</t>
+          <t>https://artportalen.se/Sighting/128960484</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128960486</v>
+        <v>128960485</v>
       </c>
       <c r="B239" t="n">
         <v>99118</v>
@@ -28030,10 +28029,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>691497</v>
+        <v>691491</v>
       </c>
       <c r="R239" t="n">
-        <v>7400703</v>
+        <v>7400689</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -28065,7 +28064,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -28075,7 +28074,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -28105,13 +28104,13 @@
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960486</t>
+          <t>https://artportalen.se/Sighting/128960485</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128960487</v>
+        <v>128960486</v>
       </c>
       <c r="B240" t="n">
         <v>99118</v>
@@ -28146,10 +28145,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>691504</v>
+        <v>691497</v>
       </c>
       <c r="R240" t="n">
-        <v>7400725</v>
+        <v>7400703</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -28181,7 +28180,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -28191,7 +28190,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -28221,13 +28220,13 @@
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960487</t>
+          <t>https://artportalen.se/Sighting/128960486</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128960488</v>
+        <v>128960487</v>
       </c>
       <c r="B241" t="n">
         <v>99118</v>
@@ -28262,10 +28261,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>691464</v>
+        <v>691504</v>
       </c>
       <c r="R241" t="n">
-        <v>7400741</v>
+        <v>7400725</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -28297,7 +28296,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -28307,7 +28306,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -28337,13 +28336,13 @@
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960488</t>
+          <t>https://artportalen.se/Sighting/128960487</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128960489</v>
+        <v>128960488</v>
       </c>
       <c r="B242" t="n">
         <v>99118</v>
@@ -28378,10 +28377,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>691434</v>
+        <v>691464</v>
       </c>
       <c r="R242" t="n">
-        <v>7400760</v>
+        <v>7400741</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -28413,7 +28412,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -28423,7 +28422,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28453,13 +28452,13 @@
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960489</t>
+          <t>https://artportalen.se/Sighting/128960488</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128960491</v>
+        <v>128960489</v>
       </c>
       <c r="B243" t="n">
         <v>99118</v>
@@ -28494,10 +28493,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>691488</v>
+        <v>691434</v>
       </c>
       <c r="R243" t="n">
-        <v>7401047</v>
+        <v>7400760</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -28529,7 +28528,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -28539,7 +28538,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -28569,13 +28568,13 @@
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960491</t>
+          <t>https://artportalen.se/Sighting/128960489</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128960492</v>
+        <v>128960491</v>
       </c>
       <c r="B244" t="n">
         <v>99118</v>
@@ -28610,10 +28609,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>691483</v>
+        <v>691488</v>
       </c>
       <c r="R244" t="n">
-        <v>7401061</v>
+        <v>7401047</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -28645,7 +28644,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -28655,7 +28654,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -28685,13 +28684,13 @@
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960492</t>
+          <t>https://artportalen.se/Sighting/128960491</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128960493</v>
+        <v>128960492</v>
       </c>
       <c r="B245" t="n">
         <v>99118</v>
@@ -28729,7 +28728,7 @@
         <v>691483</v>
       </c>
       <c r="R245" t="n">
-        <v>7401085</v>
+        <v>7401061</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28761,7 +28760,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -28771,7 +28770,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28801,13 +28800,13 @@
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960493</t>
+          <t>https://artportalen.se/Sighting/128960492</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128960495</v>
+        <v>128960493</v>
       </c>
       <c r="B246" t="n">
         <v>99118</v>
@@ -28842,10 +28841,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>691488</v>
+        <v>691483</v>
       </c>
       <c r="R246" t="n">
-        <v>7401092</v>
+        <v>7401085</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28877,7 +28876,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28887,7 +28886,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28917,13 +28916,13 @@
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960495</t>
+          <t>https://artportalen.se/Sighting/128960493</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128960496</v>
+        <v>128960495</v>
       </c>
       <c r="B247" t="n">
         <v>99118</v>
@@ -28958,10 +28957,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>691471</v>
+        <v>691488</v>
       </c>
       <c r="R247" t="n">
-        <v>7401095</v>
+        <v>7401092</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28993,7 +28992,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -29003,7 +29002,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -29033,13 +29032,13 @@
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960496</t>
+          <t>https://artportalen.se/Sighting/128960495</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128960497</v>
+        <v>128960496</v>
       </c>
       <c r="B248" t="n">
         <v>99118</v>
@@ -29074,10 +29073,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>691469</v>
+        <v>691471</v>
       </c>
       <c r="R248" t="n">
-        <v>7401129</v>
+        <v>7401095</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -29109,7 +29108,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -29119,7 +29118,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -29149,13 +29148,13 @@
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960497</t>
+          <t>https://artportalen.se/Sighting/128960496</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128960503</v>
+        <v>128960497</v>
       </c>
       <c r="B249" t="n">
         <v>99118</v>
@@ -29190,10 +29189,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>690957</v>
+        <v>691469</v>
       </c>
       <c r="R249" t="n">
-        <v>7400856</v>
+        <v>7401129</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -29220,22 +29219,22 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -29265,13 +29264,13 @@
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960503</t>
+          <t>https://artportalen.se/Sighting/128960497</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128960504</v>
+        <v>128960503</v>
       </c>
       <c r="B250" t="n">
         <v>99118</v>
@@ -29306,10 +29305,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>690949</v>
+        <v>690957</v>
       </c>
       <c r="R250" t="n">
-        <v>7400850</v>
+        <v>7400856</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29341,7 +29340,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -29351,7 +29350,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29381,13 +29380,13 @@
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960504</t>
+          <t>https://artportalen.se/Sighting/128960503</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128960505</v>
+        <v>128960504</v>
       </c>
       <c r="B251" t="n">
         <v>99118</v>
@@ -29422,10 +29421,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>690992</v>
+        <v>690949</v>
       </c>
       <c r="R251" t="n">
-        <v>7400806</v>
+        <v>7400850</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29457,7 +29456,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -29467,7 +29466,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29497,13 +29496,13 @@
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960505</t>
+          <t>https://artportalen.se/Sighting/128960504</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128960506</v>
+        <v>128960505</v>
       </c>
       <c r="B252" t="n">
         <v>99118</v>
@@ -29538,10 +29537,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>690964</v>
+        <v>690992</v>
       </c>
       <c r="R252" t="n">
-        <v>7400788</v>
+        <v>7400806</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29573,7 +29572,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -29583,7 +29582,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29613,13 +29612,13 @@
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960506</t>
+          <t>https://artportalen.se/Sighting/128960505</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128960507</v>
+        <v>128960506</v>
       </c>
       <c r="B253" t="n">
         <v>99118</v>
@@ -29654,10 +29653,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>690928</v>
+        <v>690964</v>
       </c>
       <c r="R253" t="n">
-        <v>7400812</v>
+        <v>7400788</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -29689,7 +29688,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -29699,7 +29698,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -29729,13 +29728,13 @@
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960507</t>
+          <t>https://artportalen.se/Sighting/128960506</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128960508</v>
+        <v>128960507</v>
       </c>
       <c r="B254" t="n">
         <v>99118</v>
@@ -29770,10 +29769,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>690820</v>
+        <v>690928</v>
       </c>
       <c r="R254" t="n">
-        <v>7400917</v>
+        <v>7400812</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29805,7 +29804,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -29815,7 +29814,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -29845,13 +29844,13 @@
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960508</t>
+          <t>https://artportalen.se/Sighting/128960507</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128960509</v>
+        <v>128960508</v>
       </c>
       <c r="B255" t="n">
         <v>99118</v>
@@ -29886,10 +29885,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>690841</v>
+        <v>690820</v>
       </c>
       <c r="R255" t="n">
-        <v>7400937</v>
+        <v>7400917</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29921,7 +29920,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -29931,7 +29930,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29961,13 +29960,13 @@
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960509</t>
+          <t>https://artportalen.se/Sighting/128960508</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128960510</v>
+        <v>128960509</v>
       </c>
       <c r="B256" t="n">
         <v>99118</v>
@@ -30002,10 +30001,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>690855</v>
+        <v>690841</v>
       </c>
       <c r="R256" t="n">
-        <v>7400940</v>
+        <v>7400937</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -30037,7 +30036,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -30047,7 +30046,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -30077,13 +30076,13 @@
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960510</t>
+          <t>https://artportalen.se/Sighting/128960509</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128960511</v>
+        <v>128960510</v>
       </c>
       <c r="B257" t="n">
         <v>99118</v>
@@ -30118,10 +30117,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>690875</v>
+        <v>690855</v>
       </c>
       <c r="R257" t="n">
-        <v>7400942</v>
+        <v>7400940</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -30153,7 +30152,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -30163,7 +30162,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -30193,13 +30192,13 @@
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960511</t>
+          <t>https://artportalen.se/Sighting/128960510</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128960512</v>
+        <v>128960511</v>
       </c>
       <c r="B258" t="n">
         <v>99118</v>
@@ -30234,10 +30233,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>691026</v>
+        <v>690875</v>
       </c>
       <c r="R258" t="n">
-        <v>7401085</v>
+        <v>7400942</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -30269,7 +30268,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -30279,7 +30278,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -30309,13 +30308,13 @@
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960512</t>
+          <t>https://artportalen.se/Sighting/128960511</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128960513</v>
+        <v>128960512</v>
       </c>
       <c r="B259" t="n">
         <v>99118</v>
@@ -30350,10 +30349,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>691071</v>
+        <v>691026</v>
       </c>
       <c r="R259" t="n">
-        <v>7401097</v>
+        <v>7401085</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -30385,7 +30384,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -30395,7 +30394,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -30425,13 +30424,13 @@
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960513</t>
+          <t>https://artportalen.se/Sighting/128960512</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128960515</v>
+        <v>128960513</v>
       </c>
       <c r="B260" t="n">
         <v>99118</v>
@@ -30466,10 +30465,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>691061</v>
+        <v>691071</v>
       </c>
       <c r="R260" t="n">
-        <v>7401094</v>
+        <v>7401097</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30501,7 +30500,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -30511,7 +30510,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30541,13 +30540,13 @@
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960515</t>
+          <t>https://artportalen.se/Sighting/128960513</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128960516</v>
+        <v>128960515</v>
       </c>
       <c r="B261" t="n">
         <v>99118</v>
@@ -30582,10 +30581,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>691115</v>
+        <v>691061</v>
       </c>
       <c r="R261" t="n">
-        <v>7401115</v>
+        <v>7401094</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -30617,7 +30616,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -30627,7 +30626,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -30657,51 +30656,51 @@
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960516</t>
+          <t>https://artportalen.se/Sighting/128960515</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128144827</v>
+        <v>128960516</v>
       </c>
       <c r="B262" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>691749</v>
+        <v>691115</v>
       </c>
       <c r="R262" t="n">
-        <v>7400999</v>
+        <v>7401115</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -30728,22 +30727,22 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -30758,24 +30757,28 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY262" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144827</t>
+          <t>https://artportalen.se/Sighting/128960516</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128144828</v>
+        <v>128144827</v>
       </c>
       <c r="B263" t="n">
         <v>79085</v>
@@ -30810,10 +30813,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>691820</v>
+        <v>691749</v>
       </c>
       <c r="R263" t="n">
-        <v>7400729</v>
+        <v>7400999</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30845,7 +30848,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -30855,7 +30858,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -30881,16 +30884,16 @@
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128144828</t>
+          <t>https://artportalen.se/Sighting/128144827</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128146043</v>
+        <v>128144828</v>
       </c>
       <c r="B264" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30898,21 +30901,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -30922,10 +30925,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>691657</v>
+        <v>691820</v>
       </c>
       <c r="R264" t="n">
-        <v>7400717</v>
+        <v>7400729</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30957,7 +30960,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -30967,7 +30970,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30993,13 +30996,13 @@
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146043</t>
+          <t>https://artportalen.se/Sighting/128144828</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128146044</v>
+        <v>128146043</v>
       </c>
       <c r="B265" t="n">
         <v>79917</v>
@@ -31034,10 +31037,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>691077</v>
+        <v>691657</v>
       </c>
       <c r="R265" t="n">
-        <v>7400881</v>
+        <v>7400717</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -31069,7 +31072,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -31079,7 +31082,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -31105,13 +31108,13 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146044</t>
+          <t>https://artportalen.se/Sighting/128146043</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128960360</v>
+        <v>128146044</v>
       </c>
       <c r="B266" t="n">
         <v>79917</v>
@@ -31142,14 +31145,14 @@
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>691748</v>
+        <v>691077</v>
       </c>
       <c r="R266" t="n">
-        <v>7400820</v>
+        <v>7400881</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -31176,22 +31179,22 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -31206,28 +31209,24 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY266" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960360</t>
+          <t>https://artportalen.se/Sighting/128146044</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128960361</v>
+        <v>128960360</v>
       </c>
       <c r="B267" t="n">
         <v>79917</v>
@@ -31262,10 +31261,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>691629</v>
+        <v>691748</v>
       </c>
       <c r="R267" t="n">
-        <v>7400883</v>
+        <v>7400820</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -31297,7 +31296,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -31307,7 +31306,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -31337,13 +31336,13 @@
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960361</t>
+          <t>https://artportalen.se/Sighting/128960360</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128960362</v>
+        <v>128960361</v>
       </c>
       <c r="B268" t="n">
         <v>79917</v>
@@ -31378,10 +31377,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>691425</v>
+        <v>691629</v>
       </c>
       <c r="R268" t="n">
-        <v>7400943</v>
+        <v>7400883</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -31413,7 +31412,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -31423,7 +31422,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -31453,13 +31452,13 @@
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960362</t>
+          <t>https://artportalen.se/Sighting/128960361</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128960363</v>
+        <v>128960362</v>
       </c>
       <c r="B269" t="n">
         <v>79917</v>
@@ -31494,10 +31493,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>690997</v>
+        <v>691425</v>
       </c>
       <c r="R269" t="n">
-        <v>7401042</v>
+        <v>7400943</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -31524,22 +31523,22 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -31569,13 +31568,13 @@
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960363</t>
+          <t>https://artportalen.se/Sighting/128960362</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128960365</v>
+        <v>128960363</v>
       </c>
       <c r="B270" t="n">
         <v>79917</v>
@@ -31610,10 +31609,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>691772</v>
+        <v>690997</v>
       </c>
       <c r="R270" t="n">
-        <v>7401045</v>
+        <v>7401042</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -31640,22 +31639,22 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -31685,13 +31684,13 @@
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960365</t>
+          <t>https://artportalen.se/Sighting/128960363</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128960366</v>
+        <v>128960365</v>
       </c>
       <c r="B271" t="n">
         <v>79917</v>
@@ -31726,10 +31725,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>691628</v>
+        <v>691772</v>
       </c>
       <c r="R271" t="n">
-        <v>7401071</v>
+        <v>7401045</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -31761,7 +31760,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -31771,7 +31770,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -31801,13 +31800,13 @@
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960366</t>
+          <t>https://artportalen.se/Sighting/128960365</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128960368</v>
+        <v>128960366</v>
       </c>
       <c r="B272" t="n">
         <v>79917</v>
@@ -31842,10 +31841,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>691561</v>
+        <v>691628</v>
       </c>
       <c r="R272" t="n">
-        <v>7401113</v>
+        <v>7401071</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -31877,7 +31876,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -31887,7 +31886,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -31917,13 +31916,13 @@
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960368</t>
+          <t>https://artportalen.se/Sighting/128960366</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128960369</v>
+        <v>128960368</v>
       </c>
       <c r="B273" t="n">
         <v>79917</v>
@@ -31958,10 +31957,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>691330</v>
+        <v>691561</v>
       </c>
       <c r="R273" t="n">
-        <v>7400743</v>
+        <v>7401113</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -31993,7 +31992,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -32003,7 +32002,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -32033,13 +32032,13 @@
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960369</t>
+          <t>https://artportalen.se/Sighting/128960368</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128960370</v>
+        <v>128960369</v>
       </c>
       <c r="B274" t="n">
         <v>79917</v>
@@ -32074,10 +32073,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>691375</v>
+        <v>691330</v>
       </c>
       <c r="R274" t="n">
-        <v>7400750</v>
+        <v>7400743</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -32109,7 +32108,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -32119,7 +32118,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -32149,13 +32148,13 @@
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960370</t>
+          <t>https://artportalen.se/Sighting/128960369</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128960371</v>
+        <v>128960370</v>
       </c>
       <c r="B275" t="n">
         <v>79917</v>
@@ -32190,10 +32189,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>691493</v>
+        <v>691375</v>
       </c>
       <c r="R275" t="n">
-        <v>7400837</v>
+        <v>7400750</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -32225,7 +32224,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -32235,7 +32234,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -32265,51 +32264,51 @@
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960371</t>
+          <t>https://artportalen.se/Sighting/128960370</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128146053</v>
+        <v>128960371</v>
       </c>
       <c r="B276" t="n">
-        <v>93228</v>
+        <v>79917</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>232140</v>
+        <v>229821</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Norr om Gáddoajvve, Lu lm</t>
+          <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>691789</v>
+        <v>691493</v>
       </c>
       <c r="R276" t="n">
-        <v>7400698</v>
+        <v>7400837</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -32336,22 +32335,22 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -32366,49 +32365,53 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY276" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146053</t>
+          <t>https://artportalen.se/Sighting/128960371</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>128146050</v>
+        <v>128146053</v>
       </c>
       <c r="B277" t="n">
-        <v>79350</v>
+        <v>93228</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>260591</v>
+        <v>232140</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -32418,10 +32421,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>691554</v>
+        <v>691789</v>
       </c>
       <c r="R277" t="n">
-        <v>7400883</v>
+        <v>7400698</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -32453,7 +32456,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -32463,7 +32466,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -32489,54 +32492,51 @@
       <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128146050</t>
+          <t>https://artportalen.se/Sighting/128146053</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128960420</v>
+        <v>128146050</v>
       </c>
       <c r="B278" t="n">
-        <v>90601</v>
+        <v>79350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6331677</v>
+        <v>260591</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Spökfransskivling</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Ripartites borealis</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>T.Ulvinen &amp; al.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>691867</v>
+        <v>691554</v>
       </c>
       <c r="R278" t="n">
-        <v>7400616</v>
+        <v>7400883</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -32563,22 +32563,22 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -32587,38 +32587,33 @@
       <c r="AE278" t="b">
         <v>0</v>
       </c>
-      <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="b">
         <v>0</v>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY278" t="inlineStr">
-        <is>
-          <t>Boreala Svampskogar</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr"/>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960420</t>
+          <t>https://artportalen.se/Sighting/128146050</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128960584</v>
+        <v>128960420</v>
       </c>
       <c r="B279" t="n">
-        <v>92183</v>
+        <v>90601</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32626,34 +32621,37 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>65</v>
+        <v>6331677</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Spökfransskivling</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ripartites borealis</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>T.Ulvinen &amp; al.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
           <t>Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>691877</v>
+        <v>691867</v>
       </c>
       <c r="R279" t="n">
-        <v>7400599</v>
+        <v>7400616</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -32685,7 +32683,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -32695,7 +32693,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -32704,6 +32702,7 @@
       <c r="AE279" t="b">
         <v>0</v>
       </c>
+      <c r="AF279" t="inlineStr"/>
       <c r="AG279" t="b">
         <v>0</v>
       </c>
@@ -32725,38 +32724,38 @@
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128960584</t>
+          <t>https://artportalen.se/Sighting/128960420</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128960628</v>
+        <v>128960584</v>
       </c>
       <c r="B280" t="n">
-        <v>93197</v>
+        <v>92183</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -32766,10 +32765,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>691884</v>
+        <v>691877</v>
       </c>
       <c r="R280" t="n">
-        <v>7401043</v>
+        <v>7400599</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -32801,7 +32800,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -32811,7 +32810,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -32840,6 +32839,122 @@
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128960584</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>128960628</v>
+      </c>
+      <c r="B281" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>691884</v>
+      </c>
+      <c r="R281" t="n">
+        <v>7401043</v>
+      </c>
+      <c r="S281" t="n">
+        <v>10</v>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT281" t="inlineStr"/>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128960628</t>
         </is>
@@ -33126,6 +33241,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -16527,7 +16527,7 @@
         <v>130996947</v>
       </c>
       <c r="B139" t="n">
-        <v>87347</v>
+        <v>87349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -16527,7 +16527,7 @@
         <v>130996947</v>
       </c>
       <c r="B139" t="n">
-        <v>87349</v>
+        <v>87351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -16527,7 +16527,7 @@
         <v>130996947</v>
       </c>
       <c r="B139" t="n">
-        <v>87351</v>
+        <v>87353</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -16527,7 +16527,7 @@
         <v>130996947</v>
       </c>
       <c r="B139" t="n">
-        <v>87353</v>
+        <v>87355</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
